--- a/AHR 29th/output/AHR_data 29th.xlsx
+++ b/AHR 29th/output/AHR_data 29th.xlsx
@@ -630,13 +630,13 @@
         <v>557</v>
       </c>
       <c r="V2">
-        <v>20441.83185297792</v>
+        <v>12701.96543</v>
       </c>
       <c r="W2">
-        <v>31944.90682538496</v>
+        <v>19849.64484</v>
       </c>
       <c r="X2">
-        <v>63950.50561794048</v>
+        <v>39737.00192</v>
       </c>
       <c r="Y2">
         <v>16176</v>
@@ -645,7 +645,7 @@
         <v>559</v>
       </c>
       <c r="AA2">
-        <v>21916999.37875824</v>
+        <v>22011761.6665839</v>
       </c>
       <c r="AB2">
         <v>1518370.246336654</v>
@@ -675,19 +675,19 @@
         <v>1.696402898995278</v>
       </c>
       <c r="AK2">
-        <v>14.43455536068164</v>
+        <v>14.49696588805748</v>
       </c>
       <c r="AL2">
         <v>3.455736894164194</v>
       </c>
       <c r="AM2">
-        <v>1.032197121655034</v>
+        <v>1.661160244552799</v>
       </c>
       <c r="AN2">
-        <v>0.6354690627511438</v>
+        <v>1.022688323324177</v>
       </c>
       <c r="AO2">
-        <v>0.8709860768383682</v>
+        <v>1.401716216843367</v>
       </c>
     </row>
     <row r="3">
@@ -757,16 +757,22 @@
         <v>25</v>
       </c>
       <c r="V3">
-        <v>1862.603648928</v>
+        <v>1157.36825</v>
       </c>
       <c r="W3">
-        <v>2641.69905284736</v>
+        <v>1641.47569</v>
       </c>
       <c r="X3">
-        <v>4535.751053813761</v>
+        <v>2818.38504</v>
+      </c>
+      <c r="Y3">
+        <v>1675</v>
+      </c>
+      <c r="Z3">
+        <v>136</v>
       </c>
       <c r="AA3">
-        <v>2525579.355871218</v>
+        <v>2554224.268424637</v>
       </c>
       <c r="AB3">
         <v>191272.4545454545</v>
@@ -796,16 +802,19 @@
         <v>6.443136128661689</v>
       </c>
       <c r="AK3">
-        <v>13.204093406304</v>
+        <v>13.35385314364565</v>
+      </c>
+      <c r="AL3">
+        <v>8.119402985074627</v>
       </c>
       <c r="AM3">
-        <v>1.234830610003228</v>
+        <v>1.987267233225035</v>
       </c>
       <c r="AN3">
-        <v>0.4163986805440094</v>
+        <v>0.6701287181414183</v>
       </c>
       <c r="AO3">
-        <v>0.5511766343300398</v>
+        <v>0.8870328093992438</v>
       </c>
     </row>
     <row r="4">
@@ -875,19 +884,22 @@
         <v>744</v>
       </c>
       <c r="V4">
-        <v>19231.47055944576</v>
+        <v>11949.88179</v>
       </c>
       <c r="W4">
-        <v>43137.17395473024</v>
+        <v>26804.19721</v>
       </c>
       <c r="X4">
-        <v>58810.88373025537</v>
+        <v>36543.38894</v>
       </c>
       <c r="Y4">
         <v>8544</v>
       </c>
+      <c r="Z4">
+        <v>95</v>
+      </c>
       <c r="AA4">
-        <v>32881377.0896476</v>
+        <v>32921621.43176563</v>
       </c>
       <c r="AB4">
         <v>2391661.272727272</v>
@@ -917,16 +929,19 @@
         <v>8.125876214500543</v>
       </c>
       <c r="AK4">
-        <v>13.7483419849635</v>
+        <v>13.76516892554114</v>
+      </c>
+      <c r="AL4">
+        <v>1.11189138576779</v>
       </c>
       <c r="AM4">
-        <v>0.8839677624990695</v>
+        <v>1.422608214771303</v>
       </c>
       <c r="AN4">
-        <v>0.8044106003887848</v>
+        <v>1.294573373272089</v>
       </c>
       <c r="AO4">
-        <v>1.265071960850756</v>
+        <v>2.0359359697634</v>
       </c>
     </row>
     <row r="5">
@@ -996,13 +1011,13 @@
         <v>319</v>
       </c>
       <c r="V5">
-        <v>14422.7231837568</v>
+        <v>8961.8647</v>
       </c>
       <c r="W5">
-        <v>17721.10137638016</v>
+        <v>11011.38189</v>
       </c>
       <c r="X5">
-        <v>30782.88139031424</v>
+        <v>19127.59571</v>
       </c>
       <c r="Y5">
         <v>12962</v>
@@ -1011,7 +1026,7 @@
         <v>697</v>
       </c>
       <c r="AA5">
-        <v>11324614.21751682</v>
+        <v>11375594.68451085</v>
       </c>
       <c r="AB5">
         <v>751589.2837063193</v>
@@ -1041,19 +1056,19 @@
         <v>10.33997538712333</v>
       </c>
       <c r="AK5">
-        <v>15.06755679334814</v>
+        <v>15.1353870140541</v>
       </c>
       <c r="AL5">
         <v>5.37725659620429</v>
       </c>
       <c r="AM5">
-        <v>1.04002550758884</v>
+        <v>1.673758810485055</v>
       </c>
       <c r="AN5">
-        <v>0.7110167552449139</v>
+        <v>1.144270548952871</v>
       </c>
       <c r="AO5">
-        <v>1.036290254817967</v>
+        <v>1.667747503849767</v>
       </c>
     </row>
     <row r="6">
@@ -1123,13 +1138,13 @@
         <v>1759</v>
       </c>
       <c r="V6">
-        <v>54987.40769905153</v>
+        <v>34167.59108</v>
       </c>
       <c r="W6">
-        <v>289480.9810257446</v>
+        <v>179875.14231</v>
       </c>
       <c r="X6">
-        <v>165069.7831205914</v>
+        <v>102569.60794</v>
       </c>
       <c r="Y6">
         <v>25818</v>
@@ -1138,7 +1153,7 @@
         <v>1591</v>
       </c>
       <c r="AA6">
-        <v>647806335.6056292</v>
+        <v>648566172.2669935</v>
       </c>
       <c r="AB6">
         <v>13135531.45454546</v>
@@ -1168,19 +1183,19 @@
         <v>32.35227984861115</v>
       </c>
       <c r="AK6">
-        <v>49.31710131769814</v>
+        <v>49.37494721940327</v>
       </c>
       <c r="AL6">
         <v>6.162367340615075</v>
       </c>
       <c r="AM6">
-        <v>0.8238249791284737</v>
+        <v>1.325817787210535</v>
       </c>
       <c r="AN6">
-        <v>0.634238558089147</v>
+        <v>1.02070801802942</v>
       </c>
       <c r="AO6">
-        <v>1.065609929780405</v>
+        <v>1.714932946832516</v>
       </c>
     </row>
     <row r="7">
@@ -1250,13 +1265,13 @@
         <v>294</v>
       </c>
       <c r="V7">
-        <v>16542.63311272704</v>
+        <v>10279.11566</v>
       </c>
       <c r="W7">
-        <v>39397.17936046464</v>
+        <v>24480.27231</v>
       </c>
       <c r="X7">
-        <v>32017.70814054912</v>
+        <v>19894.88148</v>
       </c>
       <c r="Y7">
         <v>8954</v>
@@ -1265,7 +1280,7 @@
         <v>437</v>
       </c>
       <c r="AA7">
-        <v>54068084.5336783</v>
+        <v>54096704.76021332</v>
       </c>
       <c r="AB7">
         <v>1927895.454545454</v>
@@ -1295,19 +1310,19 @@
         <v>12.93023055488974</v>
       </c>
       <c r="AK7">
-        <v>28.04513305231382</v>
+        <v>28.05997837313635</v>
       </c>
       <c r="AL7">
         <v>4.88050033504579</v>
       </c>
       <c r="AM7">
-        <v>0.797938267145912</v>
+        <v>1.284157162601671</v>
       </c>
       <c r="AN7">
-        <v>0.7411698114942313</v>
+        <v>1.192797189109372</v>
       </c>
       <c r="AO7">
-        <v>0.9182418638755127</v>
+        <v>1.477767034176873</v>
       </c>
     </row>
     <row r="8">
@@ -1377,17 +1392,20 @@
         <v>162</v>
       </c>
       <c r="V8">
-        <v>1942.07094740736</v>
+        <v>1206.74694</v>
       </c>
       <c r="W8">
-        <v>28264.2418403136</v>
+        <v>17562.58565</v>
       </c>
       <c r="X8">
-        <v>18882.83722609152</v>
+        <v>11733.25108</v>
       </c>
       <c r="Y8">
         <v>4362</v>
       </c>
+      <c r="Z8">
+        <v>219</v>
+      </c>
       <c r="AA8">
         <v>29865977.15888439</v>
       </c>
@@ -1421,14 +1439,17 @@
       <c r="AK8">
         <v>23.56504053713919</v>
       </c>
+      <c r="AL8">
+        <v>5.020632737276479</v>
+      </c>
       <c r="AM8">
-        <v>0.6178970967059595</v>
+        <v>0.9944089852011558</v>
       </c>
       <c r="AN8">
-        <v>0.4705592343549106</v>
+        <v>0.7572916804536695</v>
       </c>
       <c r="AO8">
-        <v>0.8579219216916996</v>
+        <v>1.380691497143007</v>
       </c>
     </row>
     <row r="9">
@@ -1498,16 +1519,22 @@
         <v>71</v>
       </c>
       <c r="V9">
-        <v>1817.94309763968</v>
+        <v>1129.61747</v>
       </c>
       <c r="W9">
-        <v>6837.90916457088</v>
+        <v>4248.87977</v>
       </c>
       <c r="X9">
-        <v>6983.33875823232</v>
+        <v>4339.24553</v>
+      </c>
+      <c r="Y9">
+        <v>874</v>
+      </c>
+      <c r="Z9">
+        <v>11</v>
       </c>
       <c r="AA9">
-        <v>18057147.9121603</v>
+        <v>18058464.12909707</v>
       </c>
       <c r="AB9">
         <v>329415.0083414444</v>
@@ -1534,16 +1561,19 @@
         <v>4.89413564020456</v>
       </c>
       <c r="AK9">
-        <v>54.8158021186568</v>
+        <v>54.819797737871</v>
+      </c>
+      <c r="AL9">
+        <v>1.25858123569794</v>
       </c>
       <c r="AM9">
-        <v>0.9351227781591122</v>
+        <v>1.504934232293698</v>
       </c>
       <c r="AN9">
-        <v>0.6580959020800917</v>
+        <v>1.059102691437183</v>
       </c>
       <c r="AO9">
-        <v>1.016705654101364</v>
+        <v>1.636229144194106</v>
       </c>
     </row>
     <row r="10">
@@ -1613,19 +1643,22 @@
         <v>1563</v>
       </c>
       <c r="V10">
-        <v>40489.17246937728</v>
+        <v>25158.80537</v>
       </c>
       <c r="W10">
-        <v>158465.6597056896</v>
+        <v>98465.99590000001</v>
       </c>
       <c r="X10">
-        <v>185981.2466746291</v>
+        <v>115563.38898</v>
       </c>
       <c r="Y10">
         <v>12881</v>
       </c>
+      <c r="Z10">
+        <v>449</v>
+      </c>
       <c r="AA10">
-        <v>281046500.0913059</v>
+        <v>281279797.6259556</v>
       </c>
       <c r="AB10">
         <v>7592382.802469552</v>
@@ -1655,16 +1688,19 @@
         <v>2.476389713976075</v>
       </c>
       <c r="AK10">
-        <v>37.0169033099715</v>
+        <v>37.04763115137774</v>
+      </c>
+      <c r="AL10">
+        <v>3.485754211629532</v>
       </c>
       <c r="AM10">
-        <v>0.7977441382490366</v>
+        <v>1.283844742426258</v>
       </c>
       <c r="AN10">
-        <v>0.8695890343430185</v>
+        <v>1.399467894885731</v>
       </c>
       <c r="AO10">
-        <v>0.8404073141494963</v>
+        <v>1.352504468582607</v>
       </c>
     </row>
     <row r="11">
@@ -1734,19 +1770,22 @@
         <v>893</v>
       </c>
       <c r="V11">
-        <v>24426.53679413376</v>
+        <v>15177.94629</v>
       </c>
       <c r="W11">
-        <v>75922.42303692288</v>
+        <v>47176.00652</v>
       </c>
       <c r="X11">
-        <v>102974.0804198093</v>
+        <v>63985.12712</v>
       </c>
       <c r="Y11">
         <v>15058</v>
       </c>
+      <c r="Z11">
+        <v>239</v>
+      </c>
       <c r="AA11">
-        <v>154283459.8396795</v>
+        <v>154333720.6383983</v>
       </c>
       <c r="AB11">
         <v>3341475.999408524</v>
@@ -1776,16 +1815,19 @@
         <v>1.752068586532401</v>
       </c>
       <c r="AK11">
-        <v>46.17224839172547</v>
+        <v>46.18728988797674</v>
+      </c>
+      <c r="AL11">
+        <v>1.587196174790809</v>
       </c>
       <c r="AM11">
-        <v>0.6836826743286279</v>
+        <v>1.100280609834732</v>
       </c>
       <c r="AN11">
-        <v>0.731009335318619</v>
+        <v>1.176445487739008</v>
       </c>
       <c r="AO11">
-        <v>0.8672085211728797</v>
+        <v>1.395636830298447</v>
       </c>
     </row>
     <row r="12">
@@ -1855,13 +1897,13 @@
         <v>33</v>
       </c>
       <c r="V12">
-        <v>509.9574199104001</v>
+        <v>316.87285</v>
       </c>
       <c r="W12">
-        <v>7047.14602914432</v>
+        <v>4378.89353</v>
       </c>
       <c r="X12">
-        <v>9236.97519566976</v>
+        <v>5739.59029</v>
       </c>
       <c r="Y12">
         <v>1190</v>
@@ -1870,7 +1912,7 @@
         <v>80</v>
       </c>
       <c r="AA12">
-        <v>6581466.145406672</v>
+        <v>6647582.078786759</v>
       </c>
       <c r="AB12">
         <v>403064.0909090909</v>
@@ -1897,19 +1939,19 @@
         <v>13.95662990577755</v>
       </c>
       <c r="AK12">
-        <v>16.3285846937208</v>
+        <v>16.49261799480442</v>
       </c>
       <c r="AL12">
         <v>6.722689075630252</v>
       </c>
       <c r="AM12">
-        <v>1.176568820403516</v>
+        <v>1.893503971703477</v>
       </c>
       <c r="AN12">
-        <v>0.7520775045786213</v>
+        <v>1.210351419528576</v>
       </c>
       <c r="AO12">
-        <v>0.3572598096341127</v>
+        <v>0.5749539310758015</v>
       </c>
     </row>
     <row r="13">
@@ -1979,16 +2021,22 @@
         <v>152</v>
       </c>
       <c r="V13">
-        <v>9603.468626400001</v>
+        <v>5967.31875</v>
       </c>
       <c r="W13">
-        <v>7134.122912970241</v>
+        <v>4432.938459999999</v>
       </c>
       <c r="X13">
-        <v>14995.9234776384</v>
+        <v>9318.03485</v>
+      </c>
+      <c r="Y13">
+        <v>4588</v>
+      </c>
+      <c r="Z13">
+        <v>235</v>
       </c>
       <c r="AA13">
-        <v>8851664.495211957</v>
+        <v>8882212.673413429</v>
       </c>
       <c r="AB13">
         <v>514179.3054618236</v>
@@ -2018,16 +2066,19 @@
         <v>11.53603651502928</v>
       </c>
       <c r="AK13">
-        <v>17.21513176665405</v>
+        <v>17.27454329465018</v>
+      </c>
+      <c r="AL13">
+        <v>5.122057541412381</v>
       </c>
       <c r="AM13">
-        <v>0.8226194417174275</v>
+        <v>1.323877662811292</v>
       </c>
       <c r="AN13">
-        <v>0.6167541621690524</v>
+        <v>0.9925696103617916</v>
       </c>
       <c r="AO13">
-        <v>1.013608799929255</v>
+        <v>1.631245240513347</v>
       </c>
     </row>
     <row r="14">
@@ -2097,13 +2148,13 @@
         <v>688</v>
       </c>
       <c r="V14">
-        <v>21327.14254467456</v>
+        <v>13252.07199</v>
       </c>
       <c r="W14">
-        <v>70010.44002919298</v>
+        <v>43502.47059</v>
       </c>
       <c r="X14">
-        <v>74216.8983308544</v>
+        <v>46116.2426</v>
       </c>
       <c r="Y14">
         <v>26873</v>
@@ -2112,7 +2163,7 @@
         <v>2472</v>
       </c>
       <c r="AA14">
-        <v>170645271.9149553</v>
+        <v>170737883.7476347</v>
       </c>
       <c r="AB14">
         <v>3717930.986931516</v>
@@ -2142,19 +2193,19 @@
         <v>11.61707878455138</v>
       </c>
       <c r="AK14">
-        <v>45.897912714026</v>
+        <v>45.92282222229956</v>
       </c>
       <c r="AL14">
         <v>9.198824098537566</v>
       </c>
       <c r="AM14">
-        <v>0.6892625193087868</v>
+        <v>1.10926049987448</v>
       </c>
       <c r="AN14">
-        <v>0.5784851514018809</v>
+        <v>0.9309816074977088</v>
       </c>
       <c r="AO14">
-        <v>0.927012601541145</v>
+        <v>1.491882168214633</v>
       </c>
     </row>
     <row r="15">
@@ -2224,13 +2275,13 @@
         <v>537</v>
       </c>
       <c r="V15">
-        <v>23386.71198720384</v>
+        <v>14531.82911</v>
       </c>
       <c r="W15">
-        <v>37651.50165034368</v>
+        <v>23395.55847</v>
       </c>
       <c r="X15">
-        <v>76092.66985769858</v>
+        <v>47281.79299</v>
       </c>
       <c r="Y15">
         <v>19381</v>
@@ -2239,7 +2290,7 @@
         <v>1018</v>
       </c>
       <c r="AA15">
-        <v>46369778.27362826</v>
+        <v>46600749.73635112</v>
       </c>
       <c r="AB15">
         <v>1911311.607090687</v>
@@ -2269,19 +2320,19 @@
         <v>2.047082254849956</v>
       </c>
       <c r="AK15">
-        <v>24.26071086556643</v>
+        <v>24.3815553484158</v>
       </c>
       <c r="AL15">
         <v>5.252566947009958</v>
       </c>
       <c r="AM15">
-        <v>0.7311844439421991</v>
+        <v>1.176727297751714</v>
       </c>
       <c r="AN15">
-        <v>0.5046279475503089</v>
+        <v>0.8121199596224044</v>
       </c>
       <c r="AO15">
-        <v>0.7057184364857316</v>
+        <v>1.135743731447693</v>
       </c>
     </row>
     <row r="16">
@@ -2351,16 +2402,22 @@
         <v>195</v>
       </c>
       <c r="V16">
-        <v>18869.1244403904</v>
+        <v>11724.73035</v>
       </c>
       <c r="W16">
-        <v>11384.47154997504</v>
+        <v>7073.98266</v>
       </c>
       <c r="X16">
-        <v>23263.55948036736</v>
+        <v>14455.30569</v>
+      </c>
+      <c r="Y16">
+        <v>23720</v>
+      </c>
+      <c r="Z16">
+        <v>4558</v>
       </c>
       <c r="AA16">
-        <v>7606534.416109472</v>
+        <v>7655303.84564644</v>
       </c>
       <c r="AB16">
         <v>778444.5674177652</v>
@@ -2390,16 +2447,19 @@
         <v>9.111872381507883</v>
       </c>
       <c r="AK16">
-        <v>9.771452887572531</v>
+        <v>9.834102730063879</v>
+      </c>
+      <c r="AL16">
+        <v>19.21585160202361</v>
       </c>
       <c r="AM16">
-        <v>0.609461241104734</v>
+        <v>0.9808327916044569</v>
       </c>
       <c r="AN16">
-        <v>0.5885209489600497</v>
+        <v>0.9471326580831625</v>
       </c>
       <c r="AO16">
-        <v>0.8382208241372729</v>
+        <v>1.348985654000376</v>
       </c>
     </row>
     <row r="17">
@@ -2469,13 +2529,13 @@
         <v>235</v>
       </c>
       <c r="V17">
-        <v>13718.84591126016</v>
+        <v>8524.495640000001</v>
       </c>
       <c r="W17">
-        <v>12234.05335646208</v>
+        <v>7601.88832</v>
       </c>
       <c r="X17">
-        <v>25268.57452703232</v>
+        <v>15701.16428</v>
       </c>
       <c r="Y17">
         <v>24907</v>
@@ -2484,7 +2544,7 @@
         <v>1305</v>
       </c>
       <c r="AA17">
-        <v>7618202.289793727</v>
+        <v>7632775.963387248</v>
       </c>
       <c r="AB17">
         <v>748273.0037459182</v>
@@ -2514,19 +2574,19 @@
         <v>7.47814507478145</v>
       </c>
       <c r="AK17">
-        <v>10.1810465587511</v>
+        <v>10.20052297113076</v>
       </c>
       <c r="AL17">
         <v>5.239490906170956</v>
       </c>
       <c r="AM17">
-        <v>0.7507920175374199</v>
+        <v>1.208282628671741</v>
       </c>
       <c r="AN17">
-        <v>0.3841735737990254</v>
+        <v>0.6182674359520188</v>
       </c>
       <c r="AO17">
-        <v>0.9300089316419372</v>
+        <v>1.496704294084362</v>
       </c>
     </row>
     <row r="18">
@@ -2596,13 +2656,13 @@
         <v>531</v>
       </c>
       <c r="V18">
-        <v>22536.66107303424</v>
+        <v>14003.63196</v>
       </c>
       <c r="W18">
-        <v>19795.45301369856</v>
+        <v>12300.32424</v>
       </c>
       <c r="X18">
-        <v>36515.03707196929</v>
+        <v>22689.39212</v>
       </c>
       <c r="Y18">
         <v>14493</v>
@@ -2611,7 +2671,7 @@
         <v>1012</v>
       </c>
       <c r="AA18">
-        <v>26964900.97156817</v>
+        <v>27097369.65386511</v>
       </c>
       <c r="AB18">
         <v>1220208.922015571</v>
@@ -2641,19 +2701,19 @@
         <v>3.544699089699647</v>
       </c>
       <c r="AK18">
-        <v>22.09859351546692</v>
+        <v>22.20715581156792</v>
       </c>
       <c r="AL18">
         <v>6.982681294417994</v>
       </c>
       <c r="AM18">
-        <v>0.5502146018798212</v>
+        <v>0.8854845682476791</v>
       </c>
       <c r="AN18">
-        <v>0.7981630927600551</v>
+        <v>1.284518984354838</v>
       </c>
       <c r="AO18">
-        <v>1.45419542900484</v>
+        <v>2.340300688496365</v>
       </c>
     </row>
     <row r="19">
@@ -2723,13 +2783,13 @@
         <v>450</v>
       </c>
       <c r="V19">
-        <v>16358.38178046336</v>
+        <v>10164.62719</v>
       </c>
       <c r="W19">
-        <v>31237.64796708864</v>
+        <v>19410.17456</v>
       </c>
       <c r="X19">
-        <v>41819.7697682688</v>
+        <v>25985.6002</v>
       </c>
       <c r="Y19">
         <v>12717</v>
@@ -2738,7 +2798,7 @@
         <v>1545</v>
       </c>
       <c r="AA19">
-        <v>33952728.5804349</v>
+        <v>34043694.0201627</v>
       </c>
       <c r="AB19">
         <v>1437266.090909091</v>
@@ -2768,19 +2828,19 @@
         <v>17.02373401833048</v>
       </c>
       <c r="AK19">
-        <v>23.62313338858452</v>
+        <v>23.68642399308926</v>
       </c>
       <c r="AL19">
         <v>12.14909176692616</v>
       </c>
       <c r="AM19">
-        <v>0.66021200293163</v>
+        <v>1.062508225646001</v>
       </c>
       <c r="AN19">
-        <v>0.7010771112816624</v>
+        <v>1.128274242578476</v>
       </c>
       <c r="AO19">
-        <v>1.076046096125193</v>
+        <v>1.731728328522502</v>
       </c>
     </row>
     <row r="20">
@@ -2850,13 +2910,13 @@
         <v>104</v>
       </c>
       <c r="V20">
-        <v>6543.3902485248</v>
+        <v>4065.8742</v>
       </c>
       <c r="W20">
-        <v>3359.58795013248</v>
+        <v>2087.55117</v>
       </c>
       <c r="X20">
-        <v>14057.19664690176</v>
+        <v>8734.73704</v>
       </c>
       <c r="Y20">
         <v>2521</v>
@@ -2865,7 +2925,7 @@
         <v>372</v>
       </c>
       <c r="AA20">
-        <v>4113565.006317522</v>
+        <v>4119944.337713346</v>
       </c>
       <c r="AB20">
         <v>322011</v>
@@ -2895,19 +2955,19 @@
         <v>11.23378031030318</v>
       </c>
       <c r="AK20">
-        <v>12.77461020374311</v>
+        <v>12.79442111515863</v>
       </c>
       <c r="AL20">
         <v>14.75604918683062</v>
       </c>
       <c r="AM20">
-        <v>0.2750867565029929</v>
+        <v>0.4427092210575526</v>
       </c>
       <c r="AN20">
-        <v>0.3869522153598439</v>
+        <v>0.6227392260760727</v>
       </c>
       <c r="AO20">
-        <v>0.7398345673916558</v>
+        <v>1.190648322024357</v>
       </c>
     </row>
     <row r="21">
@@ -2977,19 +3037,22 @@
         <v>257</v>
       </c>
       <c r="V21">
-        <v>7652.320850085121</v>
+        <v>4754.93173</v>
       </c>
       <c r="W21">
-        <v>50556.05314898689</v>
+        <v>31414.07502</v>
       </c>
       <c r="X21">
-        <v>34096.5564781248</v>
+        <v>21186.61795</v>
       </c>
       <c r="Y21">
         <v>5473</v>
       </c>
+      <c r="Z21">
+        <v>252</v>
+      </c>
       <c r="AA21">
-        <v>95024115.87709555</v>
+        <v>95042558.71330293</v>
       </c>
       <c r="AB21">
         <v>2155278.411956546</v>
@@ -3019,16 +3082,19 @@
         <v>17.34470982324148</v>
       </c>
       <c r="AK21">
-        <v>44.08902133011826</v>
+        <v>44.09757838525557</v>
+      </c>
+      <c r="AL21">
+        <v>4.604421706559473</v>
       </c>
       <c r="AM21">
-        <v>0.02613586177555209</v>
+        <v>0.04206159233331411</v>
       </c>
       <c r="AN21">
-        <v>0.6982348858597043</v>
+        <v>1.123700124149</v>
       </c>
       <c r="AO21">
-        <v>0.753741804293001</v>
+        <v>1.213029850288115</v>
       </c>
     </row>
     <row r="22">
@@ -3098,13 +3164,13 @@
         <v>170</v>
       </c>
       <c r="V22">
-        <v>1890.86701262976</v>
+        <v>1174.93029</v>
       </c>
       <c r="W22">
-        <v>54398.51419292929</v>
+        <v>33801.66962</v>
       </c>
       <c r="X22">
-        <v>41474.87862642432</v>
+        <v>25771.29478</v>
       </c>
       <c r="Y22">
         <v>5281</v>
@@ -3113,7 +3179,7 @@
         <v>450</v>
       </c>
       <c r="AA22">
-        <v>159379819.4432439</v>
+        <v>159407257.9450786</v>
       </c>
       <c r="AB22">
         <v>2474961.059727987</v>
@@ -3143,19 +3209,19 @@
         <v>19.7355797171808</v>
       </c>
       <c r="AK22">
-        <v>64.39689982870304</v>
+        <v>64.40798626649844</v>
       </c>
       <c r="AL22">
         <v>8.521113425487597</v>
       </c>
       <c r="AM22">
-        <v>0.2115431689951014</v>
+        <v>0.3404457297632526</v>
       </c>
       <c r="AN22">
-        <v>0.3106702499274633</v>
+        <v>0.4999753026992635</v>
       </c>
       <c r="AO22">
-        <v>0.4098866726801949</v>
+        <v>0.6596486573578357</v>
       </c>
     </row>
     <row r="23">
@@ -3225,13 +3291,13 @@
         <v>633</v>
       </c>
       <c r="V23">
-        <v>20735.44367837184</v>
+        <v>12884.40736</v>
       </c>
       <c r="W23">
-        <v>62593.0537750848</v>
+        <v>38893.52045</v>
       </c>
       <c r="X23">
-        <v>74851.9590722112</v>
+        <v>46510.85105</v>
       </c>
       <c r="Y23">
         <v>11341</v>
@@ -3240,7 +3306,7 @@
         <v>1292</v>
       </c>
       <c r="AA23">
-        <v>46178205.72639474</v>
+        <v>46239128.15763869</v>
       </c>
       <c r="AB23">
         <v>3174289.024659134</v>
@@ -3270,19 +3336,19 @@
         <v>11.75981746722683</v>
       </c>
       <c r="AK23">
-        <v>14.54757439151387</v>
+        <v>14.56676685658894</v>
       </c>
       <c r="AL23">
         <v>11.39229344854951</v>
       </c>
       <c r="AM23">
-        <v>0.4436847430275189</v>
+        <v>0.7140413790828795</v>
       </c>
       <c r="AN23">
-        <v>0.5735460699680707</v>
+        <v>0.9230329264266948</v>
       </c>
       <c r="AO23">
-        <v>0.8456692488026026</v>
+        <v>1.360972731544976</v>
       </c>
     </row>
     <row r="24">
@@ -3352,13 +3418,13 @@
         <v>269</v>
       </c>
       <c r="V24">
-        <v>17138.33649361152</v>
+        <v>10649.26858</v>
       </c>
       <c r="W24">
-        <v>28595.60720222976</v>
+        <v>17768.48654</v>
       </c>
       <c r="X24">
-        <v>47682.23338986624</v>
+        <v>29628.36621</v>
       </c>
       <c r="Y24">
         <v>13502</v>
@@ -3367,7 +3433,7 @@
         <v>582</v>
       </c>
       <c r="AA24">
-        <v>30985212.26279301</v>
+        <v>31030249.13349402</v>
       </c>
       <c r="AB24">
         <v>1756737.353610489</v>
@@ -3397,19 +3463,19 @@
         <v>1.759564281635701</v>
       </c>
       <c r="AK24">
-        <v>17.63793101974604</v>
+        <v>17.66356767545239</v>
       </c>
       <c r="AL24">
         <v>4.310472522589246</v>
       </c>
       <c r="AM24">
-        <v>0.4026061690743463</v>
+        <v>0.6479318225627848</v>
       </c>
       <c r="AN24">
-        <v>0.2377987623032452</v>
+        <v>0.3827000113201538</v>
       </c>
       <c r="AO24">
-        <v>0.5641514268020209</v>
+        <v>0.9079137138152714</v>
       </c>
     </row>
     <row r="25">
@@ -3479,19 +3545,22 @@
         <v>416</v>
       </c>
       <c r="V25">
-        <v>17114.3424942336</v>
+        <v>10634.3594</v>
       </c>
       <c r="W25">
-        <v>15722.75797792128</v>
+        <v>9769.66887</v>
       </c>
       <c r="X25">
-        <v>33056.4498428736</v>
+        <v>20540.32565</v>
       </c>
       <c r="Y25">
         <v>16756</v>
       </c>
+      <c r="Z25">
+        <v>1053</v>
+      </c>
       <c r="AA25">
-        <v>7569141.275461874</v>
+        <v>7639070.794064794</v>
       </c>
       <c r="AB25">
         <v>547712.2546420889</v>
@@ -3521,16 +3590,19 @@
         <v>10.71034067443024</v>
       </c>
       <c r="AK25">
-        <v>13.81955800935666</v>
+        <v>13.94723366023034</v>
+      </c>
+      <c r="AL25">
+        <v>6.284316065886847</v>
       </c>
       <c r="AM25">
-        <v>0.8413995457232346</v>
+        <v>1.354101310512413</v>
       </c>
       <c r="AN25">
-        <v>1.011272960019331</v>
+        <v>1.62748607056935</v>
       </c>
       <c r="AO25">
-        <v>1.258453348672838</v>
+        <v>2.02528434596654</v>
       </c>
     </row>
     <row r="26">
@@ -3600,13 +3672,13 @@
         <v>468</v>
       </c>
       <c r="V26">
-        <v>27070.0296539904</v>
+        <v>16820.5366</v>
       </c>
       <c r="W26">
-        <v>41838.7197134016</v>
+        <v>25997.37515</v>
       </c>
       <c r="X26">
-        <v>61167.04379736193</v>
+        <v>38007.43893</v>
       </c>
       <c r="Y26">
         <v>24617</v>
@@ -3615,7 +3687,7 @@
         <v>2213</v>
       </c>
       <c r="AA26">
-        <v>43442406.24483956</v>
+        <v>43732428.54543871</v>
       </c>
       <c r="AB26">
         <v>2023518.422012759</v>
@@ -3645,19 +3717,19 @@
         <v>8.375617940835332</v>
       </c>
       <c r="AK26">
-        <v>21.46874758947248</v>
+        <v>21.61207334200537</v>
       </c>
       <c r="AL26">
         <v>8.989722549457692</v>
       </c>
       <c r="AM26">
-        <v>0.5873654444872829</v>
+        <v>0.9452730538929418</v>
       </c>
       <c r="AN26">
-        <v>0.6596760175517341</v>
+        <v>1.061645640790778</v>
       </c>
       <c r="AO26">
-        <v>0.7651178983741967</v>
+        <v>1.231337899041123</v>
       </c>
     </row>
     <row r="27">
@@ -3727,16 +3799,22 @@
         <v>91</v>
       </c>
       <c r="V27">
-        <v>9289.377560643841</v>
+        <v>5772.151610000001</v>
       </c>
       <c r="W27">
-        <v>2974.52367134208</v>
+        <v>1848.28332</v>
       </c>
       <c r="X27">
-        <v>9783.88812669312</v>
+        <v>6079.42623</v>
+      </c>
+      <c r="Y27">
+        <v>5218</v>
+      </c>
+      <c r="Z27">
+        <v>358</v>
       </c>
       <c r="AA27">
-        <v>3176414.5464432</v>
+        <v>3186040.208913466</v>
       </c>
       <c r="AB27">
         <v>252393.9090909091</v>
@@ -3766,16 +3844,19 @@
         <v>9.662545747961152</v>
       </c>
       <c r="AK27">
-        <v>12.58514739077596</v>
+        <v>12.62328485021362</v>
+      </c>
+      <c r="AL27">
+        <v>6.860866232272901</v>
       </c>
       <c r="AM27">
-        <v>0.9580835682367448</v>
+        <v>1.541886042040396</v>
       </c>
       <c r="AN27">
-        <v>0.8404707026157304</v>
+        <v>1.35260648243041</v>
       </c>
       <c r="AO27">
-        <v>0.9301005778237297</v>
+        <v>1.496851784317153</v>
       </c>
     </row>
     <row r="28">
@@ -3845,19 +3926,22 @@
         <v>134</v>
       </c>
       <c r="V28">
-        <v>10093.08760745472</v>
+        <v>6271.553880000001</v>
       </c>
       <c r="W28">
-        <v>8126.039013523201</v>
+        <v>5049.286550000001</v>
       </c>
       <c r="X28">
-        <v>16018.97080899456</v>
+        <v>9953.726989999999</v>
       </c>
       <c r="Y28">
         <v>15348</v>
       </c>
+      <c r="Z28">
+        <v>1213</v>
+      </c>
       <c r="AA28">
-        <v>9784404.724694844</v>
+        <v>9790069.419735864</v>
       </c>
       <c r="AB28">
         <v>564093.2521141231</v>
@@ -3887,16 +3971,19 @@
         <v>28.31066229173967</v>
       </c>
       <c r="AK28">
-        <v>17.3453674335309</v>
+        <v>17.35540955869334</v>
+      </c>
+      <c r="AL28">
+        <v>7.90330987750847</v>
       </c>
       <c r="AM28">
-        <v>0.5647429430603573</v>
+        <v>0.9088656669565277</v>
       </c>
       <c r="AN28">
-        <v>0.4307141516519138</v>
+        <v>0.6931672356760976</v>
       </c>
       <c r="AO28">
-        <v>0.8365081727020801</v>
+        <v>1.346229408689056</v>
       </c>
     </row>
     <row r="29">
@@ -3966,17 +4053,20 @@
         <v>203</v>
       </c>
       <c r="V29">
-        <v>6962.7304162944</v>
+        <v>4326.4401</v>
       </c>
       <c r="W29">
-        <v>15692.94148460544</v>
+        <v>9751.141759999999</v>
       </c>
       <c r="X29">
-        <v>22046.58244723969</v>
+        <v>13699.11122</v>
       </c>
       <c r="Y29">
         <v>2090</v>
       </c>
+      <c r="Z29">
+        <v>25</v>
+      </c>
       <c r="AA29">
         <v>28023431.11818182</v>
       </c>
@@ -4010,14 +4100,17 @@
       <c r="AK29">
         <v>25.76298236159672</v>
       </c>
+      <c r="AL29">
+        <v>1.196172248803828</v>
+      </c>
       <c r="AM29">
-        <v>0.9191796346189879</v>
+        <v>1.479276229896261</v>
       </c>
       <c r="AN29">
-        <v>0.7391858315013435</v>
+        <v>1.189604282811698</v>
       </c>
       <c r="AO29">
-        <v>0.9207776329315674</v>
+        <v>1.481847958892621</v>
       </c>
     </row>
     <row r="30">
@@ -4087,13 +4180,13 @@
         <v>85</v>
       </c>
       <c r="V30">
-        <v>3677.81602776192</v>
+        <v>2285.28893</v>
       </c>
       <c r="W30">
-        <v>7746.175378149121</v>
+        <v>4813.25023</v>
       </c>
       <c r="X30">
-        <v>10325.85901978752</v>
+        <v>6416.19133</v>
       </c>
       <c r="Y30">
         <v>2537</v>
@@ -4138,13 +4231,13 @@
         <v>7.607410327158061</v>
       </c>
       <c r="AM30">
-        <v>0.5438009908334296</v>
+        <v>0.8751628617918349</v>
       </c>
       <c r="AN30">
-        <v>0.3227399171792767</v>
+        <v>0.5193995492729661</v>
       </c>
       <c r="AO30">
-        <v>0.8231760654209386</v>
+        <v>1.324773461828795</v>
       </c>
     </row>
     <row r="31">
@@ -4214,13 +4307,13 @@
         <v>260</v>
       </c>
       <c r="V31">
-        <v>3880.32615628416</v>
+        <v>2411.12289</v>
       </c>
       <c r="W31">
-        <v>72127.56107766529</v>
+        <v>44817.98862</v>
       </c>
       <c r="X31">
-        <v>49531.65644706049</v>
+        <v>30777.54442</v>
       </c>
       <c r="Y31">
         <v>6820</v>
@@ -4229,7 +4322,7 @@
         <v>442</v>
       </c>
       <c r="AA31">
-        <v>253334999.8651159</v>
+        <v>253360187.5082925</v>
       </c>
       <c r="AB31">
         <v>2988269.650570599</v>
@@ -4259,19 +4352,19 @@
         <v>15.46461734133935</v>
       </c>
       <c r="AK31">
-        <v>84.77648588933147</v>
+        <v>84.78491472813181</v>
       </c>
       <c r="AL31">
         <v>6.480938416422287</v>
       </c>
       <c r="AM31">
-        <v>0.5927336794292837</v>
+        <v>0.9539123905874414</v>
       </c>
       <c r="AN31">
-        <v>0.4353398275340158</v>
+        <v>0.7006115394029032</v>
       </c>
       <c r="AO31">
-        <v>0.5249168282467768</v>
+        <v>0.8447717480379807</v>
       </c>
     </row>
     <row r="32">
@@ -4341,17 +4434,20 @@
         <v>168</v>
       </c>
       <c r="V32">
-        <v>14461.56930392064</v>
+        <v>8986.002560000001</v>
       </c>
       <c r="W32">
-        <v>11187.64209999744</v>
+        <v>6951.67851</v>
       </c>
       <c r="X32">
-        <v>19683.90656470656</v>
+        <v>12231.01249</v>
       </c>
       <c r="Y32">
         <v>4037</v>
       </c>
+      <c r="Z32">
+        <v>201</v>
+      </c>
       <c r="AA32">
         <v>7501424.182962863</v>
       </c>
@@ -4385,14 +4481,17 @@
       <c r="AK32">
         <v>14.17505558129758</v>
       </c>
+      <c r="AL32">
+        <v>4.978944760961109</v>
+      </c>
       <c r="AM32">
-        <v>0.8574449798223672</v>
+        <v>1.379923933607248</v>
       </c>
       <c r="AN32">
-        <v>1.296072923176843</v>
+        <v>2.085827182477114</v>
       </c>
       <c r="AO32">
-        <v>0.8534891153223907</v>
+        <v>1.373557586809398</v>
       </c>
     </row>
     <row r="33">
@@ -4462,13 +4561,13 @@
         <v>567</v>
       </c>
       <c r="V33">
-        <v>17268.18850639872</v>
+        <v>10729.95488</v>
       </c>
       <c r="W33">
-        <v>90368.55726738049</v>
+        <v>56152.41817</v>
       </c>
       <c r="X33">
-        <v>85592.87444353537</v>
+        <v>53184.94644</v>
       </c>
       <c r="Y33">
         <v>17573</v>
@@ -4477,7 +4576,7 @@
         <v>1578</v>
       </c>
       <c r="AA33">
-        <v>281424126.4999145</v>
+        <v>281492864.1694436</v>
       </c>
       <c r="AB33">
         <v>4567921.572589578</v>
@@ -4507,19 +4606,19 @@
         <v>24.68940177091386</v>
       </c>
       <c r="AK33">
-        <v>61.60879122545305</v>
+        <v>61.62383913475639</v>
       </c>
       <c r="AL33">
         <v>8.979684743640814</v>
       </c>
       <c r="AM33">
-        <v>0.5559355572498368</v>
+        <v>0.8946915534466813</v>
       </c>
       <c r="AN33">
-        <v>0.4979608102722609</v>
+        <v>0.8013902422468016</v>
       </c>
       <c r="AO33">
-        <v>0.6624383205801124</v>
+        <v>1.066091136595681</v>
       </c>
     </row>
     <row r="34">
@@ -4589,13 +4688,13 @@
         <v>989</v>
       </c>
       <c r="V34">
-        <v>37557.05813456256</v>
+        <v>23336.87399</v>
       </c>
       <c r="W34">
-        <v>57590.76046179456</v>
+        <v>35785.23949</v>
       </c>
       <c r="X34">
-        <v>101606.6922617895</v>
+        <v>63135.47151</v>
       </c>
       <c r="Y34">
         <v>18817</v>
@@ -4604,7 +4703,7 @@
         <v>1336</v>
       </c>
       <c r="AA34">
-        <v>80151299.28118591</v>
+        <v>80271785.47394532</v>
       </c>
       <c r="AB34">
         <v>3302464.128111536</v>
@@ -4634,19 +4733,19 @@
         <v>5.446874253440506</v>
       </c>
       <c r="AK34">
-        <v>24.27014985535035</v>
+        <v>24.30663358025558</v>
       </c>
       <c r="AL34">
         <v>7.09996279959611</v>
       </c>
       <c r="AM34">
-        <v>0.7854715322564654</v>
+        <v>1.264093897607749</v>
       </c>
       <c r="AN34">
-        <v>0.4809799311189171</v>
+        <v>0.7740621662666425</v>
       </c>
       <c r="AO34">
-        <v>0.9733610828033288</v>
+        <v>1.566472818443041</v>
       </c>
     </row>
     <row r="35">
@@ -4716,16 +4815,22 @@
         <v>53</v>
       </c>
       <c r="V35">
-        <v>6311.088764640001</v>
+        <v>3921.528749999999</v>
       </c>
       <c r="W35">
-        <v>2336.09167617408</v>
+        <v>1451.58007</v>
       </c>
       <c r="X35">
-        <v>7278.921692064001</v>
+        <v>4522.912249999999</v>
+      </c>
+      <c r="Y35">
+        <v>4280</v>
+      </c>
+      <c r="Z35">
+        <v>455</v>
       </c>
       <c r="AA35">
-        <v>2187961.338457297</v>
+        <v>2207032.314354782</v>
       </c>
       <c r="AB35">
         <v>223378.8433501871</v>
@@ -4755,16 +4860,19 @@
         <v>8.661006087172019</v>
       </c>
       <c r="AK35">
-        <v>9.794845857569729</v>
+        <v>9.880220889562299</v>
+      </c>
+      <c r="AL35">
+        <v>10.63084112149533</v>
       </c>
       <c r="AM35">
-        <v>0.7288758202503899</v>
+        <v>1.173011928065044</v>
       </c>
       <c r="AN35">
-        <v>0.299645774666866</v>
+        <v>0.482233129585473</v>
       </c>
       <c r="AO35">
-        <v>0.728129828045607</v>
+        <v>1.17181136998623</v>
       </c>
     </row>
     <row r="36">
@@ -4834,13 +4942,13 @@
         <v>776</v>
       </c>
       <c r="V36">
-        <v>25422.96337092864</v>
+        <v>15797.09706</v>
       </c>
       <c r="W36">
-        <v>71798.04724992768</v>
+        <v>44613.23822</v>
       </c>
       <c r="X36">
-        <v>84994.9115436749</v>
+        <v>52813.38952</v>
       </c>
       <c r="Y36">
         <v>26960</v>
@@ -4849,7 +4957,7 @@
         <v>1251</v>
       </c>
       <c r="AA36">
-        <v>58781028.7687363</v>
+        <v>58814349.74473473</v>
       </c>
       <c r="AB36">
         <v>3700519.098549999</v>
@@ -4879,19 +4987,19 @@
         <v>12.70867931846173</v>
       </c>
       <c r="AK36">
-        <v>15.88453598084898</v>
+        <v>15.89354038674746</v>
       </c>
       <c r="AL36">
         <v>4.640207715133531</v>
       </c>
       <c r="AM36">
-        <v>0.4090789829753868</v>
+        <v>0.6583488067775409</v>
       </c>
       <c r="AN36">
-        <v>0.5000135989079586</v>
+        <v>0.8046938853209298</v>
       </c>
       <c r="AO36">
-        <v>0.9129958322284387</v>
+        <v>1.469324364621845</v>
       </c>
     </row>
     <row r="37">
@@ -4961,19 +5069,22 @@
         <v>390</v>
       </c>
       <c r="V37">
-        <v>19093.66867698048</v>
+        <v>11864.25567</v>
       </c>
       <c r="W37">
-        <v>23203.25980689024</v>
+        <v>14417.83721</v>
       </c>
       <c r="X37">
-        <v>31346.07668222977</v>
+        <v>19477.54904</v>
       </c>
       <c r="Y37">
         <v>22872</v>
       </c>
+      <c r="Z37">
+        <v>1815</v>
+      </c>
       <c r="AA37">
-        <v>15530460.02205965</v>
+        <v>15540300.96393642</v>
       </c>
       <c r="AB37">
         <v>1042487.883483703</v>
@@ -5003,16 +5114,19 @@
         <v>11.14383398899886</v>
       </c>
       <c r="AK37">
-        <v>14.89749690918343</v>
+        <v>14.90693677129855</v>
+      </c>
+      <c r="AL37">
+        <v>7.935466946484785</v>
       </c>
       <c r="AM37">
-        <v>0.6860913018666492</v>
+        <v>1.104156920111281</v>
       </c>
       <c r="AN37">
-        <v>0.8231602007200826</v>
+        <v>1.324747930067661</v>
       </c>
       <c r="AO37">
-        <v>1.244174841890477</v>
+        <v>2.002305316747389</v>
       </c>
     </row>
     <row r="38">
@@ -5082,19 +5196,22 @@
         <v>283</v>
       </c>
       <c r="V38">
-        <v>13932.39314624256</v>
+        <v>8657.187740000001</v>
       </c>
       <c r="W38">
-        <v>20453.7114993024</v>
+        <v>12709.3471</v>
       </c>
       <c r="X38">
-        <v>24863.33245410432</v>
+        <v>15449.35853</v>
       </c>
       <c r="Y38">
         <v>8292</v>
       </c>
+      <c r="Z38">
+        <v>401</v>
+      </c>
       <c r="AA38">
-        <v>32763022.8619495</v>
+        <v>32789632.30833888</v>
       </c>
       <c r="AB38">
         <v>1200114.001284355</v>
@@ -5124,16 +5241,19 @@
         <v>8.655853674458907</v>
       </c>
       <c r="AK38">
-        <v>27.29992552948028</v>
+        <v>27.3220979617333</v>
+      </c>
+      <c r="AL38">
+        <v>4.835986493005306</v>
       </c>
       <c r="AM38">
-        <v>1.112515261183267</v>
+        <v>1.790419760493723</v>
       </c>
       <c r="AN38">
-        <v>0.7284741451696032</v>
+        <v>1.17236549468383</v>
       </c>
       <c r="AO38">
-        <v>1.138222322057572</v>
+        <v>1.831791264669421</v>
       </c>
     </row>
     <row r="39">
@@ -5203,13 +5323,13 @@
         <v>704</v>
       </c>
       <c r="V39">
-        <v>26168.85322837632</v>
+        <v>16260.57153</v>
       </c>
       <c r="W39">
-        <v>65758.99888901376</v>
+        <v>40860.74754</v>
       </c>
       <c r="X39">
-        <v>69208.67917155457</v>
+        <v>43004.27949</v>
       </c>
       <c r="Y39">
         <v>23257</v>
@@ -5218,7 +5338,7 @@
         <v>3022</v>
       </c>
       <c r="AA39">
-        <v>150345292.892607</v>
+        <v>150418130.8190726</v>
       </c>
       <c r="AB39">
         <v>3902570.697933566</v>
@@ -5248,19 +5368,19 @@
         <v>13.19627246694982</v>
       </c>
       <c r="AK39">
-        <v>38.52468142914509</v>
+        <v>38.54334551805042</v>
       </c>
       <c r="AL39">
         <v>12.99393730919723</v>
       </c>
       <c r="AM39">
-        <v>0.4853097645955954</v>
+        <v>0.781030357793334</v>
       </c>
       <c r="AN39">
-        <v>0.5717848604030644</v>
+        <v>0.9201985343805094</v>
       </c>
       <c r="AO39">
-        <v>1.017213459969267</v>
+        <v>1.637046378520781</v>
       </c>
     </row>
     <row r="40">
@@ -5330,17 +5450,20 @@
         <v>29</v>
       </c>
       <c r="V40">
-        <v>945.62515504512</v>
+        <v>587.58423</v>
       </c>
       <c r="W40">
-        <v>7429.27834066176</v>
+        <v>4616.339540000001</v>
       </c>
       <c r="X40">
-        <v>3798.0601281216</v>
+        <v>2360.00515</v>
       </c>
       <c r="Y40">
         <v>782</v>
       </c>
+      <c r="Z40">
+        <v>120</v>
+      </c>
       <c r="AA40">
         <v>15648631.51379426</v>
       </c>
@@ -5374,14 +5497,17 @@
       <c r="AK40">
         <v>31.55234693354824</v>
       </c>
+      <c r="AL40">
+        <v>15.34526854219949</v>
+      </c>
       <c r="AM40">
-        <v>0.3172504436873675</v>
+        <v>0.5105650980456027</v>
       </c>
       <c r="AN40">
-        <v>0.5114897875345341</v>
+        <v>0.823163020629977</v>
       </c>
       <c r="AO40">
-        <v>0.7635476801769983</v>
+        <v>1.228810877806771</v>
       </c>
     </row>
     <row r="41">
@@ -5418,10 +5544,10 @@
         <v>39008000</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>7.880000000000001</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>528.727</v>
       </c>
       <c r="M41">
         <v>9.643000000000001</v>
@@ -5430,10 +5556,10 @@
         <v>1407.964</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>287.194</v>
       </c>
       <c r="Q41">
         <v>32.889</v>
@@ -5451,13 +5577,13 @@
         <v>568</v>
       </c>
       <c r="V41">
-        <v>18453.2676172416</v>
+        <v>11466.3289</v>
       </c>
       <c r="W41">
-        <v>34071.509533248</v>
+        <v>21171.0545</v>
       </c>
       <c r="X41">
-        <v>45313.3270446912</v>
+        <v>28156.39605</v>
       </c>
       <c r="Y41">
         <v>9481</v>
@@ -5466,7 +5592,7 @@
         <v>527</v>
       </c>
       <c r="AA41">
-        <v>34079677.46686053</v>
+        <v>34107602.18790133</v>
       </c>
       <c r="AB41">
         <v>1580429.882662839</v>
@@ -5483,6 +5609,12 @@
       <c r="AF41">
         <v>432.1621191135097</v>
       </c>
+      <c r="AG41">
+        <v>1.490372158032406</v>
+      </c>
+      <c r="AH41">
+        <v>1.11074743901335</v>
+      </c>
       <c r="AI41">
         <v>0.6848896704745293</v>
       </c>
@@ -5490,19 +5622,19 @@
         <v>2.762539530547191</v>
       </c>
       <c r="AK41">
-        <v>21.56354915881511</v>
+        <v>21.58121822553368</v>
       </c>
       <c r="AL41">
         <v>5.558485391836304</v>
       </c>
       <c r="AM41">
-        <v>1.186781683019542</v>
+        <v>1.909939980877402</v>
       </c>
       <c r="AN41">
-        <v>0.7631009120575777</v>
+        <v>1.22809187421439</v>
       </c>
       <c r="AO41">
-        <v>1.253494362574168</v>
+        <v>2.017303631442561</v>
       </c>
     </row>
     <row r="42">
@@ -5572,19 +5704,22 @@
         <v>85</v>
       </c>
       <c r="V42">
-        <v>7106.364271733761</v>
+        <v>4415.69004</v>
       </c>
       <c r="W42">
-        <v>2449.54877054976</v>
+        <v>1522.07904</v>
       </c>
       <c r="X42">
-        <v>7092.21545036928</v>
+        <v>4406.89837</v>
       </c>
       <c r="Y42">
         <v>5889</v>
       </c>
+      <c r="Z42">
+        <v>985</v>
+      </c>
       <c r="AA42">
-        <v>2697682.056507108</v>
+        <v>2728776.083423266</v>
       </c>
       <c r="AB42">
         <v>209864.8756239886</v>
@@ -5614,16 +5749,19 @@
         <v>7.400009845000902</v>
       </c>
       <c r="AK42">
-        <v>12.85437617174443</v>
+        <v>13.00253830141814</v>
+      </c>
+      <c r="AL42">
+        <v>16.72609950755646</v>
       </c>
       <c r="AM42">
-        <v>0.6332351998755789</v>
+        <v>1.019093269508563</v>
       </c>
       <c r="AN42">
-        <v>0.4082384527398354</v>
+        <v>0.6569961044861375</v>
       </c>
       <c r="AO42">
-        <v>1.198497149372051</v>
+        <v>1.928794196359015</v>
       </c>
     </row>
     <row r="43">
@@ -5693,13 +5831,13 @@
         <v>685</v>
       </c>
       <c r="V43">
-        <v>24107.35302366336</v>
+        <v>14979.61469</v>
       </c>
       <c r="W43">
-        <v>51325.22763916416</v>
+        <v>31892.01789</v>
       </c>
       <c r="X43">
-        <v>58794.72427496448</v>
+        <v>36533.34792</v>
       </c>
       <c r="Y43">
         <v>20373</v>
@@ -5708,7 +5846,7 @@
         <v>898</v>
       </c>
       <c r="AA43">
-        <v>67150303.39657459</v>
+        <v>67195148.4232662</v>
       </c>
       <c r="AB43">
         <v>2224172.370018231</v>
@@ -5738,19 +5876,19 @@
         <v>4.945399049077275</v>
       </c>
       <c r="AK43">
-        <v>30.19114179357608</v>
+        <v>30.2113043615929</v>
       </c>
       <c r="AL43">
         <v>4.407794630147745</v>
       </c>
       <c r="AM43">
-        <v>0.6554016936032335</v>
+        <v>1.054766783190202</v>
       </c>
       <c r="AN43">
-        <v>0.9332642484657874</v>
+        <v>1.501943218682924</v>
       </c>
       <c r="AO43">
-        <v>1.16507052026721</v>
+        <v>1.874999251368912</v>
       </c>
     </row>
     <row r="44">
@@ -5820,13 +5958,13 @@
         <v>2151</v>
       </c>
       <c r="V44">
-        <v>76029.21025337088</v>
+        <v>47242.36102</v>
       </c>
       <c r="W44">
-        <v>224707.4678941171</v>
+        <v>139626.74723</v>
       </c>
       <c r="X44">
-        <v>182610.5356146931</v>
+        <v>113468.92623</v>
       </c>
       <c r="Y44">
         <v>56313</v>
@@ -5835,7 +5973,7 @@
         <v>708</v>
       </c>
       <c r="AA44">
-        <v>380260801.0480261</v>
+        <v>380348748.5783882</v>
       </c>
       <c r="AB44">
         <v>10254521.33486466</v>
@@ -5865,19 +6003,19 @@
         <v>13.45924821384413</v>
       </c>
       <c r="AK44">
-        <v>37.08225753601642</v>
+        <v>37.09083399975277</v>
       </c>
       <c r="AL44">
         <v>1.257258537105109</v>
       </c>
       <c r="AM44">
-        <v>0.9364821726113252</v>
+        <v>1.507121965599</v>
       </c>
       <c r="AN44">
-        <v>0.6314876907734269</v>
+        <v>1.01628092622007</v>
       </c>
       <c r="AO44">
-        <v>1.177916702757279</v>
+        <v>1.895673178082211</v>
       </c>
     </row>
     <row r="45">
@@ -5947,19 +6085,22 @@
         <v>108</v>
       </c>
       <c r="V45">
-        <v>10114.08079182336</v>
+        <v>6284.59844</v>
       </c>
       <c r="W45">
-        <v>24471.99582144768</v>
+        <v>15206.19322</v>
       </c>
       <c r="X45">
-        <v>21071.8510345728</v>
+        <v>13093.4412</v>
       </c>
       <c r="Y45">
         <v>3109</v>
       </c>
+      <c r="Z45">
+        <v>75</v>
+      </c>
       <c r="AA45">
-        <v>18198641.44662096</v>
+        <v>18217018.48442919</v>
       </c>
       <c r="AB45">
         <v>1124073.909090909</v>
@@ -5989,16 +6130,19 @@
         <v>3.50212439655184</v>
       </c>
       <c r="AK45">
-        <v>16.1898975676244</v>
+        <v>16.20624617038051</v>
+      </c>
+      <c r="AL45">
+        <v>2.412351238340302</v>
       </c>
       <c r="AM45">
-        <v>0.6723300060542723</v>
+        <v>1.082010261263407</v>
       </c>
       <c r="AN45">
-        <v>0.4249755547475723</v>
+        <v>0.6839318591796771</v>
       </c>
       <c r="AO45">
-        <v>0.5125320970749238</v>
+        <v>0.8248404552349461</v>
       </c>
     </row>
     <row r="46">
@@ -6068,19 +6212,22 @@
         <v>44</v>
       </c>
       <c r="V46">
-        <v>3104.73289412352</v>
+        <v>1929.19158</v>
       </c>
       <c r="W46">
-        <v>1870.94483059968</v>
+        <v>1162.55122</v>
       </c>
       <c r="X46">
-        <v>6567.297890503681</v>
+        <v>4080.72972</v>
       </c>
       <c r="Y46">
         <v>2856</v>
       </c>
+      <c r="Z46">
+        <v>75</v>
+      </c>
       <c r="AA46">
-        <v>1074011.560549445</v>
+        <v>1086680.835630157</v>
       </c>
       <c r="AB46">
         <v>86794.63636363637</v>
@@ -6110,16 +6257,19 @@
         <v>8.84378368811443</v>
       </c>
       <c r="AK46">
-        <v>12.37416971308857</v>
+        <v>12.52013812325199</v>
+      </c>
+      <c r="AL46">
+        <v>2.626050420168067</v>
       </c>
       <c r="AM46">
-        <v>0.5475511285423854</v>
+        <v>0.8811981234129169</v>
       </c>
       <c r="AN46">
-        <v>0.3741425126766748</v>
+        <v>0.6021240079211306</v>
       </c>
       <c r="AO46">
-        <v>0.6699863586761313</v>
+        <v>1.07823852641728</v>
       </c>
     </row>
     <row r="47">
@@ -6189,13 +6339,13 @@
         <v>502</v>
       </c>
       <c r="V47">
-        <v>23133.91442921856</v>
+        <v>14374.74799</v>
       </c>
       <c r="W47">
-        <v>60608.73870640512</v>
+        <v>37660.52423</v>
       </c>
       <c r="X47">
-        <v>57445.40472092928</v>
+        <v>35694.91962</v>
       </c>
       <c r="Y47">
         <v>14068</v>
@@ -6204,7 +6354,7 @@
         <v>498</v>
       </c>
       <c r="AA47">
-        <v>89975595.6272217</v>
+        <v>90006831.12309851</v>
       </c>
       <c r="AB47">
         <v>2742717.336842092</v>
@@ -6234,19 +6384,19 @@
         <v>5.950046138388304</v>
       </c>
       <c r="AK47">
-        <v>32.8052746882104</v>
+        <v>32.81666320989918</v>
       </c>
       <c r="AL47">
         <v>3.53994882001706</v>
       </c>
       <c r="AM47">
-        <v>0.7521424899031994</v>
+        <v>1.210456003270775</v>
       </c>
       <c r="AN47">
-        <v>0.3728835227784015</v>
+        <v>0.6000978600822839</v>
       </c>
       <c r="AO47">
-        <v>0.8738732061140907</v>
+        <v>1.406362601020476</v>
       </c>
     </row>
     <row r="48">
@@ -6316,13 +6466,13 @@
         <v>380</v>
       </c>
       <c r="V48">
-        <v>14574.31205877504</v>
+        <v>9056.05766</v>
       </c>
       <c r="W48">
-        <v>45084.5535647232</v>
+        <v>28014.2428</v>
       </c>
       <c r="X48">
-        <v>36585.99526982401</v>
+        <v>22733.4835</v>
       </c>
       <c r="Y48">
         <v>8421</v>
@@ -6331,7 +6481,7 @@
         <v>456</v>
       </c>
       <c r="AA48">
-        <v>82363552.0436902</v>
+        <v>82442151.73031788</v>
       </c>
       <c r="AB48">
         <v>2440490.965981094</v>
@@ -6361,19 +6511,19 @@
         <v>19.08112270743927</v>
       </c>
       <c r="AK48">
-        <v>33.74876333974852</v>
+        <v>33.78096984562103</v>
       </c>
       <c r="AL48">
         <v>5.415033843961525</v>
       </c>
       <c r="AM48">
-        <v>0.8027823167787569</v>
+        <v>1.291952904813992</v>
       </c>
       <c r="AN48">
-        <v>0.6631983159614896</v>
+        <v>1.067314230602727</v>
       </c>
       <c r="AO48">
-        <v>1.038648797709277</v>
+        <v>1.671543210700639</v>
       </c>
     </row>
     <row r="49">
@@ -6443,13 +6593,13 @@
         <v>163</v>
       </c>
       <c r="V49">
-        <v>5774.6048494464</v>
+        <v>3588.1731</v>
       </c>
       <c r="W49">
-        <v>7378.15186361088</v>
+        <v>4584.57102</v>
       </c>
       <c r="X49">
-        <v>12536.22026143872</v>
+        <v>7789.646129999999</v>
       </c>
       <c r="Y49">
         <v>7323</v>
@@ -6458,7 +6608,7 @@
         <v>1442</v>
       </c>
       <c r="AA49">
-        <v>4161980.144332835</v>
+        <v>4198064.686293007</v>
       </c>
       <c r="AB49">
         <v>336739.3991298127</v>
@@ -6488,19 +6638,19 @@
         <v>3.390736813019529</v>
       </c>
       <c r="AK49">
-        <v>12.35964711907203</v>
+        <v>12.46680577663755</v>
       </c>
       <c r="AL49">
         <v>19.69138331284993</v>
       </c>
       <c r="AM49">
-        <v>0.7792741005354515</v>
+        <v>1.254120098052126</v>
       </c>
       <c r="AN49">
-        <v>0.7047835414782464</v>
+        <v>1.134239163776767</v>
       </c>
       <c r="AO49">
-        <v>1.300232419347211</v>
+        <v>2.092521242681919</v>
       </c>
     </row>
     <row r="50">
@@ -6570,19 +6720,22 @@
         <v>322</v>
       </c>
       <c r="V50">
-        <v>23245.31296340352</v>
+        <v>14443.96783</v>
       </c>
       <c r="W50">
-        <v>34561.20980226816</v>
+        <v>21475.34014</v>
       </c>
       <c r="X50">
-        <v>50419.28263071744</v>
+        <v>31329.08976</v>
       </c>
       <c r="Y50">
         <v>14412</v>
       </c>
+      <c r="Z50">
+        <v>943</v>
+      </c>
       <c r="AA50">
-        <v>29041156.2198891</v>
+        <v>29096458.64023131</v>
       </c>
       <c r="AB50">
         <v>1721161.893948415</v>
@@ -6612,16 +6765,19 @@
         <v>19.37292198373957</v>
       </c>
       <c r="AK50">
-        <v>16.87299510987169</v>
+        <v>16.90512597480465</v>
+      </c>
+      <c r="AL50">
+        <v>6.54315847904524</v>
       </c>
       <c r="AM50">
-        <v>0.5721583538556345</v>
+        <v>0.9207996138274422</v>
       </c>
       <c r="AN50">
-        <v>0.361677153997649</v>
+        <v>0.5820629577231925</v>
       </c>
       <c r="AO50">
-        <v>0.6386445486707991</v>
+        <v>1.027798772536058</v>
       </c>
     </row>
     <row r="51">
@@ -6691,16 +6847,22 @@
         <v>40</v>
       </c>
       <c r="V51">
-        <v>6903.047942334721</v>
+        <v>4289.35513</v>
       </c>
       <c r="W51">
-        <v>2218.03646068224</v>
+        <v>1378.22396</v>
       </c>
       <c r="X51">
-        <v>6198.03378095616</v>
+        <v>3851.27964</v>
+      </c>
+      <c r="Y51">
+        <v>3131</v>
+      </c>
+      <c r="Z51">
+        <v>204</v>
       </c>
       <c r="AA51">
-        <v>841126.546758425</v>
+        <v>851541.3564718456</v>
       </c>
       <c r="AB51">
         <v>73483.09090909091</v>
@@ -6730,16 +6892,19 @@
         <v>6.881288329604618</v>
       </c>
       <c r="AK51">
-        <v>11.44653193479598</v>
+        <v>11.58826263208394</v>
+      </c>
+      <c r="AL51">
+        <v>6.51549025870329</v>
       </c>
       <c r="AM51">
-        <v>1.071990237039728</v>
+        <v>1.725201056038463</v>
       </c>
       <c r="AN51">
-        <v>1.12712304072361</v>
+        <v>1.813928702850297</v>
       </c>
       <c r="AO51">
-        <v>0.6453659565861428</v>
+        <v>1.038615830036169</v>
       </c>
     </row>
     <row r="52">
@@ -6776,10 +6941,10 @@
         <v>39399383000</v>
       </c>
       <c r="K52">
-        <v>630.1407000000002</v>
+        <v>638.0207000000001</v>
       </c>
       <c r="L52">
-        <v>28588.1255</v>
+        <v>29116.8525</v>
       </c>
       <c r="M52">
         <v>980.803</v>
@@ -6788,10 +6953,10 @@
         <v>90323.34430000001</v>
       </c>
       <c r="O52">
-        <v>860.9029</v>
+        <v>864.0929000000001</v>
       </c>
       <c r="P52">
-        <v>18806.9625</v>
+        <v>19094.1565</v>
       </c>
       <c r="Q52">
         <v>8224.396699999999</v>
@@ -6809,16 +6974,22 @@
         <v>21305</v>
       </c>
       <c r="V52">
-        <v>828230.3647308979</v>
+        <v>514638.4891799999</v>
       </c>
       <c r="W52">
-        <v>2092913.378615853</v>
+        <v>1300476.08132</v>
       </c>
       <c r="X52">
-        <v>2298500.041460706</v>
+        <v>1428221.711120001</v>
+      </c>
+      <c r="Y52">
+        <v>618923</v>
+      </c>
+      <c r="Z52">
+        <v>42093</v>
       </c>
       <c r="AA52">
-        <v>3603000403.953233</v>
+        <v>3606339440.525678</v>
       </c>
       <c r="AB52">
         <v>102496440.1305783</v>
@@ -6836,10 +7007,10 @@
         <v>19929.18004386406</v>
       </c>
       <c r="AG52">
-        <v>2.20420432952136</v>
+        <v>2.191241996366194</v>
       </c>
       <c r="AH52">
-        <v>4.577575459088623</v>
+        <v>4.525431118153872</v>
       </c>
       <c r="AI52">
         <v>1.085879854871583</v>
@@ -6848,16 +7019,19 @@
         <v>13.0744730448242</v>
       </c>
       <c r="AK52">
-        <v>35.15244431282772</v>
+        <v>35.18502141080489</v>
+      </c>
+      <c r="AL52">
+        <v>6.801007556675064</v>
       </c>
       <c r="AM52">
-        <v>0.7359063685114152</v>
+        <v>1.184326498725635</v>
       </c>
       <c r="AN52">
-        <v>0.6220515446563828</v>
+        <v>1.001094921083481</v>
       </c>
       <c r="AO52">
-        <v>0.9269088368804461</v>
+        <v>1.491715175180524</v>
       </c>
     </row>
   </sheetData>
@@ -7024,28 +7198,31 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.9396674647851146</v>
+        <v>0.9396674647851151</v>
+      </c>
+      <c r="C2">
+        <v>0.5081213136974758</v>
       </c>
       <c r="D2">
         <v>0.235191891090527</v>
       </c>
       <c r="E2">
-        <v>1.402620178084548</v>
+        <v>1.402620178084547</v>
       </c>
       <c r="F2">
-        <v>0.7854922820323976</v>
+        <v>0.7901388763690342</v>
       </c>
       <c r="G2">
-        <v>0.4106273587186716</v>
+        <v>0.4120209483119893</v>
       </c>
       <c r="H2">
         <v>0.1297492367898402</v>
       </c>
       <c r="I2">
-        <v>1.021569785028301</v>
+        <v>1.021569785028302</v>
       </c>
       <c r="J2">
-        <v>0.8392836707650408</v>
+        <v>0.8489543281514237</v>
       </c>
       <c r="K2">
         <v>1.499839526846228</v>
@@ -7060,11 +7237,14 @@
         <v>0.3529880884958834</v>
       </c>
       <c r="O2">
-        <v>0.6958142274963096</v>
+        <v>0.6825848373053484</v>
       </c>
       <c r="P2">
         <v>25</v>
       </c>
+      <c r="Q2">
+        <v>8</v>
+      </c>
       <c r="R2">
         <v>5</v>
       </c>
@@ -7072,7 +7252,7 @@
         <v>44</v>
       </c>
       <c r="T2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U2">
         <v>14</v>
@@ -7084,7 +7264,7 @@
         <v>28</v>
       </c>
       <c r="X2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Y2">
         <v>41</v>
@@ -7099,7 +7279,7 @@
         <v>5</v>
       </c>
       <c r="AC2">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -7109,7 +7289,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.5946395291526725</v>
+        <v>0.5946395291526728</v>
+      </c>
+      <c r="C3">
+        <v>1.193852957435047</v>
       </c>
       <c r="D3">
         <v>10.63993265327039</v>
@@ -7118,19 +7301,19 @@
         <v>1.677972447094094</v>
       </c>
       <c r="F3">
-        <v>4.926573267724375</v>
+        <v>4.955716504352496</v>
       </c>
       <c r="G3">
-        <v>0.3756237628541127</v>
+        <v>0.3795323296163987</v>
       </c>
       <c r="H3">
         <v>0.4928027390910673</v>
       </c>
       <c r="I3">
-        <v>0.6693957825858712</v>
+        <v>0.6693957825858716</v>
       </c>
       <c r="J3">
-        <v>0.2944461094819594</v>
+        <v>0.2978388687393364</v>
       </c>
       <c r="K3">
         <v>0.7291676258689515</v>
@@ -7145,11 +7328,14 @@
         <v>0.8254884232784953</v>
       </c>
       <c r="O3">
-        <v>2.045780418931519</v>
+        <v>1.983050965173927</v>
       </c>
       <c r="P3">
         <v>5</v>
       </c>
+      <c r="Q3">
+        <v>37</v>
+      </c>
       <c r="R3">
         <v>50</v>
       </c>
@@ -7157,7 +7343,7 @@
         <v>50</v>
       </c>
       <c r="T3">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="U3">
         <v>10</v>
@@ -7169,7 +7355,7 @@
         <v>11</v>
       </c>
       <c r="X3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y3">
         <v>21</v>
@@ -7194,28 +7380,31 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.364828892028275</v>
+        <v>1.364828892028276</v>
+      </c>
+      <c r="C4">
+        <v>0.163489214870301</v>
       </c>
       <c r="D4">
         <v>1.838497197288097</v>
       </c>
       <c r="E4">
-        <v>1.20119596775219</v>
+        <v>1.201195967752191</v>
       </c>
       <c r="F4">
-        <v>2.340360629829937</v>
+        <v>2.354205077060045</v>
       </c>
       <c r="G4">
-        <v>0.3911062873072101</v>
+        <v>0.3912224115149758</v>
       </c>
       <c r="H4">
         <v>0.6215069767356584</v>
       </c>
       <c r="I4">
-        <v>1.293157467896227</v>
+        <v>1.293157467896228</v>
       </c>
       <c r="J4">
-        <v>0.5956640800234869</v>
+        <v>0.6025276273983944</v>
       </c>
       <c r="K4">
         <v>2.368469444871838</v>
@@ -7230,11 +7419,14 @@
         <v>1.189016709410239</v>
       </c>
       <c r="O4">
-        <v>1.243657829398236</v>
+        <v>1.162169791266301</v>
       </c>
       <c r="P4">
         <v>48</v>
       </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
       <c r="R4">
         <v>42</v>
       </c>
@@ -7242,7 +7434,7 @@
         <v>39</v>
       </c>
       <c r="T4">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U4">
         <v>11</v>
@@ -7254,7 +7446,7 @@
         <v>43</v>
       </c>
       <c r="X4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y4">
         <v>48</v>
@@ -7269,7 +7461,7 @@
         <v>36</v>
       </c>
       <c r="AC4">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -7279,7 +7471,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.118006662128337</v>
+        <v>1.118006662128338</v>
+      </c>
+      <c r="C5">
+        <v>0.7906558772937418</v>
       </c>
       <c r="D5">
         <v>0.8376843868161776</v>
@@ -7288,10 +7483,10 @@
         <v>1.41325792531541</v>
       </c>
       <c r="F5">
-        <v>1.088407588094001</v>
+        <v>1.094846083608819</v>
       </c>
       <c r="G5">
-        <v>0.4286346821080018</v>
+        <v>0.4301656331920324</v>
       </c>
       <c r="H5">
         <v>0.7908521706132258</v>
@@ -7300,7 +7495,7 @@
         <v>1.143019033314474</v>
       </c>
       <c r="J5">
-        <v>1.131211762419345</v>
+        <v>1.144246165168814</v>
       </c>
       <c r="K5">
         <v>0.3045603641223378</v>
@@ -7315,11 +7510,14 @@
         <v>0.760324411820306</v>
       </c>
       <c r="O5">
-        <v>0.8668387076187922</v>
+        <v>0.8625941706205821</v>
       </c>
       <c r="P5">
         <v>37</v>
       </c>
+      <c r="Q5">
+        <v>22</v>
+      </c>
       <c r="R5">
         <v>25</v>
       </c>
@@ -7327,7 +7525,7 @@
         <v>45</v>
       </c>
       <c r="T5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U5">
         <v>17</v>
@@ -7339,7 +7537,7 @@
         <v>35</v>
       </c>
       <c r="X5">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -7354,7 +7552,7 @@
         <v>26</v>
       </c>
       <c r="AC5">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -7364,28 +7562,31 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.149638332683032</v>
+        <v>1.149638332683033</v>
+      </c>
+      <c r="C6">
+        <v>0.9060962348978461</v>
       </c>
       <c r="D6">
         <v>1.81057994012489</v>
       </c>
       <c r="E6">
-        <v>1.11946983254799</v>
+        <v>1.119469832547991</v>
       </c>
       <c r="F6">
-        <v>3.308450130618278</v>
+        <v>3.328021329459594</v>
       </c>
       <c r="G6">
-        <v>1.402949418789108</v>
+        <v>1.403294505435226</v>
       </c>
       <c r="H6">
         <v>2.474461474485083</v>
       </c>
       <c r="I6">
-        <v>1.019591645640067</v>
+        <v>1.019591645640068</v>
       </c>
       <c r="J6">
-        <v>2.218588196892497</v>
+        <v>2.244151909235503</v>
       </c>
       <c r="K6">
         <v>1.14554833149121</v>
@@ -7400,11 +7601,14 @@
         <v>2.14684746469207</v>
       </c>
       <c r="O6">
-        <v>1.72747664564131</v>
+        <v>1.667791998494155</v>
       </c>
       <c r="P6">
         <v>39</v>
       </c>
+      <c r="Q6">
+        <v>25</v>
+      </c>
       <c r="R6">
         <v>39</v>
       </c>
@@ -7412,7 +7616,7 @@
         <v>36</v>
       </c>
       <c r="T6">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U6">
         <v>46</v>
@@ -7424,7 +7628,7 @@
         <v>27</v>
       </c>
       <c r="X6">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Y6">
         <v>35</v>
@@ -7449,7 +7653,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.9906495950193953</v>
+        <v>0.9906495950193958</v>
+      </c>
+      <c r="C7">
+        <v>0.7176143085233994</v>
       </c>
       <c r="D7">
         <v>1.293409155354229</v>
@@ -7458,19 +7665,19 @@
         <v>1.084293194472517</v>
       </c>
       <c r="F7">
-        <v>3.270424933617674</v>
+        <v>3.28977119369247</v>
       </c>
       <c r="G7">
-        <v>0.7978145929977245</v>
+        <v>0.7974978342494194</v>
       </c>
       <c r="H7">
         <v>0.9889676249711987</v>
       </c>
       <c r="I7">
-        <v>1.191492598742197</v>
+        <v>1.191492598742198</v>
       </c>
       <c r="J7">
-        <v>1.631186274531008</v>
+        <v>1.649981640321909</v>
       </c>
       <c r="K7">
         <v>1.078767124681877</v>
@@ -7485,11 +7692,14 @@
         <v>0.6627254886268301</v>
       </c>
       <c r="O7">
-        <v>1.258682232448945</v>
+        <v>1.219971228079087</v>
       </c>
       <c r="P7">
         <v>28</v>
       </c>
+      <c r="Q7">
+        <v>16</v>
+      </c>
       <c r="R7">
         <v>33</v>
       </c>
@@ -7497,7 +7707,7 @@
         <v>33</v>
       </c>
       <c r="T7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U7">
         <v>35</v>
@@ -7509,7 +7719,7 @@
         <v>39</v>
       </c>
       <c r="X7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y7">
         <v>33</v>
@@ -7524,7 +7734,7 @@
         <v>18</v>
       </c>
       <c r="AC7">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -7534,7 +7744,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.9255731389713306</v>
+        <v>0.925573138971331</v>
+      </c>
+      <c r="C8">
+        <v>0.7382189617402822</v>
       </c>
       <c r="D8">
         <v>1.22989502405996</v>
@@ -7543,19 +7756,19 @@
         <v>0.8396409151286952</v>
       </c>
       <c r="F8">
-        <v>0.01537371902138749</v>
+        <v>0.01546466254479549</v>
       </c>
       <c r="G8">
-        <v>0.6703670540640017</v>
+        <v>0.6697463747997793</v>
       </c>
       <c r="H8">
         <v>0.6234066076961315</v>
       </c>
       <c r="I8">
-        <v>0.756463412714206</v>
+        <v>0.7564634127142066</v>
       </c>
       <c r="J8">
-        <v>0.3447531117592547</v>
+        <v>0.3487255341270985</v>
       </c>
       <c r="K8">
         <v>0.5519123946396213</v>
@@ -7570,11 +7783,14 @@
         <v>0.714706534302798</v>
       </c>
       <c r="O8">
-        <v>0.6734327548861169</v>
+        <v>0.6786811313077473</v>
       </c>
       <c r="P8">
         <v>23</v>
       </c>
+      <c r="Q8">
+        <v>18</v>
+      </c>
       <c r="R8">
         <v>32</v>
       </c>
@@ -7594,7 +7810,7 @@
         <v>15</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Y8">
         <v>16</v>
@@ -7609,7 +7825,7 @@
         <v>22</v>
       </c>
       <c r="AC8">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -7621,6 +7837,9 @@
       <c r="B9">
         <v>1.096877722649763</v>
       </c>
+      <c r="C9">
+        <v>0.1850580557674379</v>
+      </c>
       <c r="D9">
         <v>0.2357686109564302</v>
       </c>
@@ -7628,16 +7847,16 @@
         <v>1.270708908323039</v>
       </c>
       <c r="G9">
-        <v>1.559373841285159</v>
+        <v>1.558043608893088</v>
       </c>
       <c r="H9">
         <v>0.3743275635985961</v>
       </c>
       <c r="I9">
-        <v>1.057944325889617</v>
+        <v>1.057944325889618</v>
       </c>
       <c r="J9">
-        <v>1.700492623167784</v>
+        <v>1.720086572293158</v>
       </c>
       <c r="K9">
         <v>2.095477938150119</v>
@@ -7652,11 +7871,14 @@
         <v>0.7220843616682547</v>
       </c>
       <c r="O9">
-        <v>1.082140823836452</v>
+        <v>1.008905902891809</v>
       </c>
       <c r="P9">
         <v>35</v>
       </c>
+      <c r="Q9">
+        <v>4</v>
+      </c>
       <c r="R9">
         <v>6</v>
       </c>
@@ -7673,7 +7895,7 @@
         <v>29</v>
       </c>
       <c r="X9">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y9">
         <v>46</v>
@@ -7688,7 +7910,7 @@
         <v>23</v>
       </c>
       <c r="AC9">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -7698,7 +7920,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.9066774214581074</v>
+        <v>0.9066774214581077</v>
+      </c>
+      <c r="C10">
+        <v>0.5125349711173792</v>
       </c>
       <c r="D10">
         <v>0.263209844680736</v>
@@ -7707,19 +7932,19 @@
         <v>1.084029398825161</v>
       </c>
       <c r="F10">
-        <v>0.07864740530344617</v>
+        <v>0.07911264550558872</v>
       </c>
       <c r="G10">
-        <v>1.053039241896001</v>
+        <v>1.052937575874286</v>
       </c>
       <c r="H10">
         <v>0.1894064644506959</v>
       </c>
       <c r="I10">
-        <v>1.397937263902099</v>
+        <v>1.3979372639021</v>
       </c>
       <c r="J10">
-        <v>0.2573988724933252</v>
+        <v>0.2603647544641434</v>
       </c>
       <c r="K10">
         <v>0.6527913909429419</v>
@@ -7734,11 +7959,14 @@
         <v>0.5389037474330423</v>
       </c>
       <c r="O10">
-        <v>0.7400729884199306</v>
+        <v>0.7228261760236764</v>
       </c>
       <c r="P10">
         <v>20</v>
       </c>
+      <c r="Q10">
+        <v>9</v>
+      </c>
       <c r="R10">
         <v>7</v>
       </c>
@@ -7758,7 +7986,7 @@
         <v>46</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
         <v>19</v>
@@ -7773,7 +8001,7 @@
         <v>13</v>
       </c>
       <c r="AC10">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
@@ -7783,28 +8011,31 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.9355920309180669</v>
+        <v>0.9355920309180672</v>
+      </c>
+      <c r="C11">
+        <v>0.2333766227377597</v>
       </c>
       <c r="D11">
         <v>0.1935561488903614</v>
       </c>
       <c r="E11">
-        <v>0.9290348658234541</v>
+        <v>0.929034865823454</v>
       </c>
       <c r="F11">
-        <v>0.3439194286596548</v>
+        <v>0.3459538904946386</v>
       </c>
       <c r="G11">
-        <v>1.313486139991592</v>
+        <v>1.312697506950875</v>
       </c>
       <c r="H11">
         <v>0.1340068223419524</v>
       </c>
       <c r="I11">
-        <v>1.175158781612581</v>
+        <v>1.175158781612582</v>
       </c>
       <c r="J11">
-        <v>0.3537150383902588</v>
+        <v>0.3577907246782636</v>
       </c>
       <c r="K11">
         <v>0.809400540264168</v>
@@ -7819,11 +8050,14 @@
         <v>0.3957012822449435</v>
       </c>
       <c r="O11">
-        <v>0.6556164726425244</v>
+        <v>0.6235458315023327</v>
       </c>
       <c r="P11">
         <v>24</v>
       </c>
+      <c r="Q11">
+        <v>5</v>
+      </c>
       <c r="R11">
         <v>3</v>
       </c>
@@ -7843,7 +8077,7 @@
         <v>37</v>
       </c>
       <c r="X11">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Y11">
         <v>24</v>
@@ -7858,7 +8092,7 @@
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -7868,7 +8102,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.3854314420353213</v>
+        <v>0.3854314420353214</v>
+      </c>
+      <c r="C12">
+        <v>0.9884842826019296</v>
       </c>
       <c r="D12">
         <v>3.859573524270966</v>
@@ -7877,16 +8114,16 @@
         <v>1.598802335116992</v>
       </c>
       <c r="G12">
-        <v>0.4645078034520128</v>
+        <v>0.4687397458777656</v>
       </c>
       <c r="H12">
         <v>1.067471695259074</v>
       </c>
       <c r="I12">
-        <v>1.209027629686321</v>
+        <v>1.209027629686322</v>
       </c>
       <c r="J12">
-        <v>3.572378424195119</v>
+        <v>3.613541202643324</v>
       </c>
       <c r="K12">
         <v>0.8948901261695145</v>
@@ -7901,11 +8138,14 @@
         <v>0.3839553101465879</v>
       </c>
       <c r="O12">
-        <v>1.32572070543016</v>
+        <v>1.301400563600637</v>
       </c>
       <c r="P12">
         <v>1</v>
       </c>
+      <c r="Q12">
+        <v>30</v>
+      </c>
       <c r="R12">
         <v>48</v>
       </c>
@@ -7922,7 +8162,7 @@
         <v>40</v>
       </c>
       <c r="X12">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y12">
         <v>29</v>
@@ -7937,7 +8177,7 @@
         <v>6</v>
       </c>
       <c r="AC12">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -7947,7 +8187,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>1.093536666821088</v>
+        <v>1.093536666821089</v>
+      </c>
+      <c r="C13">
+        <v>0.753132164422487</v>
       </c>
       <c r="D13">
         <v>0.5978279955129476</v>
@@ -7956,19 +8199,19 @@
         <v>1.117831665706895</v>
       </c>
       <c r="F13">
-        <v>0.4803359149477122</v>
+        <v>0.4831773510676245</v>
       </c>
       <c r="G13">
-        <v>0.4897278725045007</v>
+        <v>0.4909629894198494</v>
       </c>
       <c r="H13">
         <v>0.8823328080205924</v>
       </c>
       <c r="I13">
-        <v>0.9914840136113534</v>
+        <v>0.991484013611354</v>
       </c>
       <c r="J13">
-        <v>0.33427098937279</v>
+        <v>0.3381226313444309</v>
       </c>
       <c r="K13">
         <v>0.544227916268833</v>
@@ -7983,11 +8226,14 @@
         <v>1.845385329631515</v>
       </c>
       <c r="O13">
-        <v>0.9248074550668266</v>
+        <v>0.9122115246331777</v>
       </c>
       <c r="P13">
         <v>34</v>
       </c>
+      <c r="Q13">
+        <v>19</v>
+      </c>
       <c r="R13">
         <v>19</v>
       </c>
@@ -8007,7 +8253,7 @@
         <v>25</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y13">
         <v>14</v>
@@ -8022,7 +8268,7 @@
         <v>43</v>
       </c>
       <c r="AC13">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
@@ -8034,6 +8280,9 @@
       <c r="B14">
         <v>1.000111946996911</v>
       </c>
+      <c r="C14">
+        <v>1.352567839673857</v>
+      </c>
       <c r="D14">
         <v>2.321055992716456</v>
       </c>
@@ -8041,19 +8290,19 @@
         <v>0.9366171415298672</v>
       </c>
       <c r="F14">
-        <v>0.6014907314479032</v>
+        <v>0.60504886115868</v>
       </c>
       <c r="G14">
-        <v>1.305681969241527</v>
+        <v>1.305181022518782</v>
       </c>
       <c r="H14">
         <v>0.888531319367418</v>
       </c>
       <c r="I14">
-        <v>0.9299633709959395</v>
+        <v>0.9299633709959401</v>
       </c>
       <c r="J14">
-        <v>1.017518751505177</v>
+        <v>1.029243125006996</v>
       </c>
       <c r="K14">
         <v>0.8566220360385857</v>
@@ -8068,11 +8317,14 @@
         <v>0.9284378720032486</v>
       </c>
       <c r="O14">
-        <v>1.061395781983413</v>
+        <v>1.084930675381897</v>
       </c>
       <c r="P14">
         <v>30</v>
       </c>
+      <c r="Q14">
+        <v>41</v>
+      </c>
       <c r="R14">
         <v>46</v>
       </c>
@@ -8092,7 +8344,7 @@
         <v>23</v>
       </c>
       <c r="X14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Y14">
         <v>27</v>
@@ -8107,7 +8359,7 @@
         <v>32</v>
       </c>
       <c r="AC14">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -8117,28 +8369,31 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.7613676862342355</v>
+        <v>0.7613676862342358</v>
+      </c>
+      <c r="C15">
+        <v>0.7723218807270197</v>
       </c>
       <c r="D15">
         <v>0.2044410705351135</v>
       </c>
       <c r="E15">
-        <v>0.9935835253352031</v>
+        <v>0.993583525335203</v>
       </c>
       <c r="F15">
-        <v>0.9712328410779868</v>
+        <v>0.9769781871776732</v>
       </c>
       <c r="G15">
-        <v>0.6901571523637486</v>
+        <v>0.6929526932426002</v>
       </c>
       <c r="H15">
         <v>0.1565709186008332</v>
       </c>
       <c r="I15">
-        <v>0.8112317249032186</v>
+        <v>0.811231724903219</v>
       </c>
       <c r="J15">
-        <v>0.6653528371059196</v>
+        <v>0.6730193741217584</v>
       </c>
       <c r="K15">
         <v>0.5662203057184089</v>
@@ -8153,11 +8408,14 @@
         <v>0.2593388302164586</v>
       </c>
       <c r="O15">
-        <v>0.8320589988461269</v>
+        <v>0.8287105608365323</v>
       </c>
       <c r="P15">
         <v>11</v>
       </c>
+      <c r="Q15">
+        <v>21</v>
+      </c>
       <c r="R15">
         <v>4</v>
       </c>
@@ -8165,10 +8423,10 @@
         <v>27</v>
       </c>
       <c r="T15">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U15">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="V15">
         <v>4</v>
@@ -8177,7 +8435,7 @@
         <v>19</v>
       </c>
       <c r="X15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y15">
         <v>17</v>
@@ -8192,7 +8450,7 @@
         <v>3</v>
       </c>
       <c r="AC15">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -8202,28 +8460,31 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.9043185163260966</v>
+        <v>0.9043185163260969</v>
+      </c>
+      <c r="C16">
+        <v>2.825441883704952</v>
       </c>
       <c r="D16">
         <v>1.729328633816181</v>
       </c>
       <c r="E16">
-        <v>0.8281776964881371</v>
+        <v>0.8281776964881369</v>
       </c>
       <c r="F16">
-        <v>0.7976249358738358</v>
+        <v>0.8023433011519795</v>
       </c>
       <c r="G16">
-        <v>0.2779736396312777</v>
+        <v>0.2794968522328068</v>
       </c>
       <c r="H16">
         <v>0.6969208128135619</v>
       </c>
       <c r="I16">
-        <v>0.9460967567971313</v>
+        <v>0.9460967567971321</v>
       </c>
       <c r="J16">
-        <v>0.9437336731708669</v>
+        <v>0.9546078571150259</v>
       </c>
       <c r="K16">
         <v>0.8470905795282542</v>
@@ -8238,11 +8499,14 @@
         <v>0.6839033119456941</v>
       </c>
       <c r="O16">
-        <v>0.9023704530794969</v>
+        <v>1.051615621729442</v>
       </c>
       <c r="P16">
         <v>19</v>
       </c>
+      <c r="Q16">
+        <v>49</v>
+      </c>
       <c r="R16">
         <v>38</v>
       </c>
@@ -8250,7 +8514,7 @@
         <v>17</v>
       </c>
       <c r="T16">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U16">
         <v>1</v>
@@ -8262,7 +8526,7 @@
         <v>24</v>
       </c>
       <c r="X16">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="Y16">
         <v>26</v>
@@ -8277,7 +8541,7 @@
         <v>19</v>
       </c>
       <c r="AC16">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -8289,6 +8553,9 @@
       <c r="B17">
         <v>1.003344551953917</v>
       </c>
+      <c r="C17">
+        <v>0.7703992184258776</v>
+      </c>
       <c r="D17">
         <v>0.3373722148931939</v>
       </c>
@@ -8296,19 +8563,19 @@
         <v>1.020227639904945</v>
       </c>
       <c r="F17">
-        <v>0.2830125498798091</v>
+        <v>0.2846867159302585</v>
       </c>
       <c r="G17">
-        <v>0.2896255653845347</v>
+        <v>0.2899109496633218</v>
       </c>
       <c r="H17">
         <v>0.57196531356511</v>
       </c>
       <c r="I17">
-        <v>0.6175912223017473</v>
+        <v>0.6175912223017477</v>
       </c>
       <c r="J17">
-        <v>0.5430447272084106</v>
+        <v>0.549301967382674</v>
       </c>
       <c r="K17">
         <v>1.100235532324545</v>
@@ -8323,11 +8590,14 @@
         <v>1.942408494794886</v>
       </c>
       <c r="O17">
-        <v>0.8394965447628405</v>
+        <v>0.8348134266218049</v>
       </c>
       <c r="P17">
         <v>31</v>
       </c>
+      <c r="Q17">
+        <v>20</v>
+      </c>
       <c r="R17">
         <v>8</v>
       </c>
@@ -8347,7 +8617,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y17">
         <v>34</v>
@@ -8362,7 +8632,7 @@
         <v>45</v>
       </c>
       <c r="AC17">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
@@ -8372,7 +8642,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>1.568865643679696</v>
+        <v>1.568865643679697</v>
+      </c>
+      <c r="C18">
+        <v>1.026712768105164</v>
       </c>
       <c r="D18">
         <v>0.5188103213897088</v>
@@ -8381,19 +8654,19 @@
         <v>0.7476693033555211</v>
       </c>
       <c r="F18">
-        <v>0.5646926983753501</v>
+        <v>0.5680331486308534</v>
       </c>
       <c r="G18">
-        <v>0.6286502673557404</v>
+        <v>0.6311536819115983</v>
       </c>
       <c r="H18">
         <v>0.2711160195555943</v>
       </c>
       <c r="I18">
-        <v>1.283114075700841</v>
+        <v>1.283114075700842</v>
       </c>
       <c r="J18">
-        <v>1.04220164767419</v>
+        <v>1.054210430179149</v>
       </c>
       <c r="K18">
         <v>0.1056872857145292</v>
@@ -8408,11 +8681,14 @@
         <v>0.7354265487458066</v>
       </c>
       <c r="O18">
-        <v>0.7467359629782671</v>
+        <v>0.7696459208585147</v>
       </c>
       <c r="P18">
         <v>50</v>
       </c>
+      <c r="Q18">
+        <v>32</v>
+      </c>
       <c r="R18">
         <v>15</v>
       </c>
@@ -8432,7 +8708,7 @@
         <v>42</v>
       </c>
       <c r="X18">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y18">
         <v>1</v>
@@ -8447,7 +8723,7 @@
         <v>24</v>
       </c>
       <c r="AC18">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -8457,19 +8733,22 @@
         </is>
       </c>
       <c r="B19">
-        <v>1.160897440299172</v>
+        <v>1.160897440299173</v>
+      </c>
+      <c r="C19">
+        <v>1.786366456099884</v>
       </c>
       <c r="D19">
         <v>2.67197024088364</v>
       </c>
       <c r="E19">
-        <v>0.897141309249845</v>
+        <v>0.8971413092498451</v>
       </c>
       <c r="F19">
-        <v>2.064094353085754</v>
+        <v>2.076304541970763</v>
       </c>
       <c r="G19">
-        <v>0.672019651844354</v>
+        <v>0.6731962364478044</v>
       </c>
       <c r="H19">
         <v>1.302058902103874</v>
@@ -8478,7 +8757,7 @@
         <v>1.127040222476954</v>
       </c>
       <c r="J19">
-        <v>2.946636470773769</v>
+        <v>2.980589129146233</v>
       </c>
       <c r="K19">
         <v>0.152286605939051</v>
@@ -8493,11 +8772,14 @@
         <v>0.9626668352297851</v>
       </c>
       <c r="O19">
-        <v>1.290353026438343</v>
+        <v>1.33214940040161</v>
       </c>
       <c r="P19">
         <v>40</v>
       </c>
+      <c r="Q19">
+        <v>44</v>
+      </c>
       <c r="R19">
         <v>47</v>
       </c>
@@ -8505,7 +8787,7 @@
         <v>21</v>
       </c>
       <c r="T19">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U19">
         <v>29</v>
@@ -8517,7 +8799,7 @@
         <v>33</v>
       </c>
       <c r="X19">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y19">
         <v>2</v>
@@ -8532,7 +8814,7 @@
         <v>33</v>
       </c>
       <c r="AC19">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -8542,7 +8824,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.7981740360590397</v>
+        <v>0.7981740360590401</v>
+      </c>
+      <c r="C20">
+        <v>2.169685750804355</v>
       </c>
       <c r="D20">
         <v>1.830413955670263</v>
@@ -8551,19 +8836,19 @@
         <v>0.3738067344891116</v>
       </c>
       <c r="F20">
-        <v>0.08772069682519988</v>
+        <v>0.08823961025362868</v>
       </c>
       <c r="G20">
-        <v>0.363406029181346</v>
+        <v>0.3636326084834958</v>
       </c>
       <c r="H20">
         <v>0.8592147669576871</v>
       </c>
       <c r="I20">
-        <v>0.6220581215236654</v>
+        <v>0.6220581215236657</v>
       </c>
       <c r="J20">
-        <v>0.1406155216166975</v>
+        <v>0.1422357658560773</v>
       </c>
       <c r="K20">
         <v>0.4713419486192916</v>
@@ -8578,11 +8863,14 @@
         <v>0.6082340142477216</v>
       </c>
       <c r="O20">
-        <v>0.6826824318380665</v>
+        <v>0.797249282294701</v>
       </c>
       <c r="P20">
         <v>13</v>
       </c>
+      <c r="Q20">
+        <v>46</v>
+      </c>
       <c r="R20">
         <v>41</v>
       </c>
@@ -8617,7 +8905,7 @@
         <v>15</v>
       </c>
       <c r="AC20">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -8627,28 +8915,31 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.8131779246271439</v>
+        <v>0.8131779246271441</v>
+      </c>
+      <c r="C21">
+        <v>0.6770205250015225</v>
       </c>
       <c r="D21">
         <v>0.9969135788695546</v>
       </c>
       <c r="E21">
-        <v>0.03551519988666423</v>
+        <v>0.03551519988666422</v>
       </c>
       <c r="F21">
-        <v>0.6865694421812787</v>
+        <v>0.6906308566021727</v>
       </c>
       <c r="G21">
-        <v>1.254223488351546</v>
+        <v>1.253305429898466</v>
       </c>
       <c r="H21">
         <v>1.326608710253737</v>
       </c>
       <c r="I21">
-        <v>1.12247110686849</v>
+        <v>1.122471106868491</v>
       </c>
       <c r="J21">
-        <v>1.51116364383174</v>
+        <v>1.528576047245872</v>
       </c>
       <c r="K21">
         <v>1.210376185983448</v>
@@ -8663,11 +8954,14 @@
         <v>1.690702025055796</v>
       </c>
       <c r="O21">
-        <v>1.042630965191562</v>
+        <v>1.016088297437094</v>
       </c>
       <c r="P21">
         <v>14</v>
       </c>
+      <c r="Q21">
+        <v>13</v>
+      </c>
       <c r="R21">
         <v>30</v>
       </c>
@@ -8675,7 +8969,7 @@
         <v>1</v>
       </c>
       <c r="T21">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U21">
         <v>43</v>
@@ -8687,7 +8981,7 @@
         <v>32</v>
       </c>
       <c r="X21">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Y21">
         <v>36</v>
@@ -8702,7 +8996,7 @@
         <v>42</v>
       </c>
       <c r="AC21">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22">
@@ -8712,7 +9006,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.4422081831258478</v>
+        <v>0.442208183125848</v>
+      </c>
+      <c r="C22">
+        <v>1.252919270340213</v>
       </c>
       <c r="D22">
         <v>0.5283741971192827</v>
@@ -8721,19 +9018,19 @@
         <v>0.2874593535900621</v>
       </c>
       <c r="F22">
-        <v>0.9137641149646667</v>
+        <v>0.9191695037364453</v>
       </c>
       <c r="G22">
-        <v>1.831932347452821</v>
+        <v>1.830551288131931</v>
       </c>
       <c r="H22">
         <v>1.509474198273218</v>
       </c>
       <c r="I22">
-        <v>0.499428467940025</v>
+        <v>0.4994284679400253</v>
       </c>
       <c r="J22">
-        <v>0.559219183088474</v>
+        <v>0.5656627936481932</v>
       </c>
       <c r="K22">
         <v>1.292981409076074</v>
@@ -8748,11 +9045,14 @@
         <v>0.4696098979516736</v>
       </c>
       <c r="O22">
-        <v>0.7924045610046894</v>
+        <v>0.8286339955697763</v>
       </c>
       <c r="P22">
         <v>2</v>
       </c>
+      <c r="Q22">
+        <v>38</v>
+      </c>
       <c r="R22">
         <v>17</v>
       </c>
@@ -8760,7 +9060,7 @@
         <v>2</v>
       </c>
       <c r="T22">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U22">
         <v>49</v>
@@ -8772,7 +9072,7 @@
         <v>3</v>
       </c>
       <c r="X22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y22">
         <v>38</v>
@@ -8787,7 +9087,7 @@
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
@@ -8797,7 +9097,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.9123542846443681</v>
+        <v>0.9123542846443682</v>
+      </c>
+      <c r="C23">
+        <v>1.675089073731169</v>
       </c>
       <c r="D23">
         <v>0.52368998063394</v>
@@ -8806,19 +9109,19 @@
         <v>0.6029092314080667</v>
       </c>
       <c r="F23">
-        <v>1.042740437318175</v>
+        <v>1.048908787945489</v>
       </c>
       <c r="G23">
-        <v>0.4138424703002861</v>
+        <v>0.4140047745463546</v>
       </c>
       <c r="H23">
         <v>0.8994486758211797</v>
       </c>
       <c r="I23">
-        <v>0.9220233835845448</v>
+        <v>0.9220233835845454</v>
       </c>
       <c r="J23">
-        <v>1.34466027031906</v>
+        <v>1.360154136372099</v>
       </c>
       <c r="K23">
         <v>0.5078059877002319</v>
@@ -8833,11 +9136,14 @@
         <v>0.6916684680623589</v>
       </c>
       <c r="O23">
-        <v>0.8211587284642142</v>
+        <v>0.8885244874021663</v>
       </c>
       <c r="P23">
         <v>21</v>
       </c>
+      <c r="Q23">
+        <v>43</v>
+      </c>
       <c r="R23">
         <v>16</v>
       </c>
@@ -8845,7 +9151,7 @@
         <v>7</v>
       </c>
       <c r="T23">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="U23">
         <v>15</v>
@@ -8857,7 +9163,7 @@
         <v>22</v>
       </c>
       <c r="X23">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Y23">
         <v>12</v>
@@ -8872,7 +9178,7 @@
         <v>21</v>
       </c>
       <c r="AC23">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24">
@@ -8882,28 +9188,31 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.6086374456205405</v>
+        <v>0.6086374456205406</v>
+      </c>
+      <c r="C24">
+        <v>0.6337991079510854</v>
       </c>
       <c r="D24">
         <v>0.6653816999576683</v>
       </c>
       <c r="E24">
-        <v>0.5470888502959071</v>
+        <v>0.547088850295907</v>
       </c>
       <c r="F24">
-        <v>0.2296149805867606</v>
+        <v>0.2309732723138808</v>
       </c>
       <c r="G24">
-        <v>0.5017554643649536</v>
+        <v>0.5020195232857847</v>
       </c>
       <c r="H24">
         <v>0.1345801299680113</v>
       </c>
       <c r="I24">
-        <v>0.382281443308052</v>
+        <v>0.3822814433080522</v>
       </c>
       <c r="J24">
-        <v>0.40879965584603</v>
+        <v>0.4135100553796638</v>
       </c>
       <c r="K24">
         <v>1.068919053911298</v>
@@ -8918,11 +9227,14 @@
         <v>1.366345514227359</v>
       </c>
       <c r="O24">
-        <v>0.7069506650692476</v>
+        <v>0.7018107568433571</v>
       </c>
       <c r="P24">
         <v>6</v>
       </c>
+      <c r="Q24">
+        <v>11</v>
+      </c>
       <c r="R24">
         <v>22</v>
       </c>
@@ -8942,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="X24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y24">
         <v>32</v>
@@ -8957,7 +9269,7 @@
         <v>38</v>
       </c>
       <c r="AC24">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25">
@@ -8969,6 +9281,9 @@
       <c r="B25">
         <v>1.357688370852327</v>
       </c>
+      <c r="C25">
+        <v>0.9240272141322511</v>
+      </c>
       <c r="D25">
         <v>1.409724875163748</v>
       </c>
@@ -8976,19 +9291,19 @@
         <v>1.143351357897894</v>
       </c>
       <c r="F25">
-        <v>0.8227569166842332</v>
+        <v>0.8276239506665428</v>
       </c>
       <c r="G25">
-        <v>0.3931322068637392</v>
+        <v>0.3963969070073471</v>
       </c>
       <c r="H25">
         <v>0.8191795292790139</v>
       </c>
       <c r="I25">
-        <v>1.625706050738852</v>
+        <v>1.625706050738853</v>
       </c>
       <c r="J25">
-        <v>1.056924457023163</v>
+        <v>1.069102883296896</v>
       </c>
       <c r="K25">
         <v>0.3547102048853112</v>
@@ -9003,11 +9318,14 @@
         <v>0.4938316664593561</v>
       </c>
       <c r="O25">
-        <v>0.8865213129974309</v>
+        <v>0.8909687023462364</v>
       </c>
       <c r="P25">
         <v>47</v>
       </c>
+      <c r="Q25">
+        <v>26</v>
+      </c>
       <c r="R25">
         <v>34</v>
       </c>
@@ -9015,7 +9333,7 @@
         <v>37</v>
       </c>
       <c r="T25">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U25">
         <v>12</v>
@@ -9027,7 +9345,7 @@
         <v>48</v>
       </c>
       <c r="X25">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -9042,7 +9360,7 @@
         <v>12</v>
       </c>
       <c r="AC25">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
@@ -9052,28 +9370,31 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.8254510777448577</v>
+        <v>0.8254510777448579</v>
+      </c>
+      <c r="C26">
+        <v>1.321822167457298</v>
       </c>
       <c r="D26">
         <v>0.4283564961395795</v>
       </c>
       <c r="E26">
-        <v>0.7981524139754361</v>
+        <v>0.7981524139754359</v>
       </c>
       <c r="F26">
-        <v>0.5084792327429719</v>
+        <v>0.5114871511875014</v>
       </c>
       <c r="G26">
-        <v>0.6107327103179044</v>
+        <v>0.6142407330003378</v>
       </c>
       <c r="H26">
         <v>0.6406084522198771</v>
       </c>
       <c r="I26">
-        <v>1.060484493959636</v>
+        <v>1.060484493959637</v>
       </c>
       <c r="J26">
-        <v>0.700403613814797</v>
+        <v>0.7084740238767646</v>
       </c>
       <c r="K26">
         <v>0.1842100386110946</v>
@@ -9088,11 +9409,14 @@
         <v>0.8091947193177004</v>
       </c>
       <c r="O26">
-        <v>0.6365103243441551</v>
+        <v>0.6903486469827762</v>
       </c>
       <c r="P26">
         <v>16</v>
       </c>
+      <c r="Q26">
+        <v>40</v>
+      </c>
       <c r="R26">
         <v>13</v>
       </c>
@@ -9103,7 +9427,7 @@
         <v>23</v>
       </c>
       <c r="U26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V26">
         <v>22</v>
@@ -9112,7 +9436,7 @@
         <v>30</v>
       </c>
       <c r="X26">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -9127,7 +9451,7 @@
         <v>27</v>
       </c>
       <c r="AC26">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
@@ -9137,7 +9461,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.003443424872316</v>
+        <v>1.003443424872317</v>
+      </c>
+      <c r="C27">
+        <v>1.008801442300867</v>
       </c>
       <c r="D27">
         <v>0.8720214844490485</v>
@@ -9146,10 +9473,10 @@
         <v>1.301909603221328</v>
       </c>
       <c r="F27">
-        <v>0.6771626394046668</v>
+        <v>0.681168407707187</v>
       </c>
       <c r="G27">
-        <v>0.3580162812798605</v>
+        <v>0.3587687130506382</v>
       </c>
       <c r="H27">
         <v>0.7390390201451579</v>
@@ -9158,7 +9485,7 @@
         <v>1.351127104876817</v>
       </c>
       <c r="J27">
-        <v>0.4003367475011637</v>
+        <v>0.4049496330595513</v>
       </c>
       <c r="K27">
         <v>0.8923365303699624</v>
@@ -9173,11 +9500,14 @@
         <v>0.8963057430743514</v>
       </c>
       <c r="O27">
-        <v>0.8622712342585871</v>
+        <v>0.8742636414642769</v>
       </c>
       <c r="P27">
         <v>32</v>
       </c>
+      <c r="Q27">
+        <v>31</v>
+      </c>
       <c r="R27">
         <v>26</v>
       </c>
@@ -9185,7 +9515,7 @@
         <v>43</v>
       </c>
       <c r="T27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U27">
         <v>7</v>
@@ -9197,7 +9527,7 @@
         <v>45</v>
       </c>
       <c r="X27">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y27">
         <v>28</v>
@@ -9212,7 +9542,7 @@
         <v>30</v>
       </c>
       <c r="AC27">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -9222,28 +9552,31 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.9024708141928892</v>
+        <v>0.9024708141928895</v>
+      </c>
+      <c r="C28">
+        <v>1.162079267174394</v>
       </c>
       <c r="D28">
         <v>2.034286467301081</v>
       </c>
       <c r="E28">
-        <v>0.76741140887626</v>
+        <v>0.7674114088762599</v>
       </c>
       <c r="F28">
-        <v>0.2569084444335262</v>
+        <v>0.2584281911582811</v>
       </c>
       <c r="G28">
-        <v>0.4934327547516029</v>
+        <v>0.4932613044641691</v>
       </c>
       <c r="H28">
         <v>2.165338686666767</v>
       </c>
       <c r="I28">
-        <v>0.6924091023515382</v>
+        <v>0.6924091023515386</v>
       </c>
       <c r="J28">
-        <v>0.2792584340233658</v>
+        <v>0.2824761930859674</v>
       </c>
       <c r="K28">
         <v>0.8329701163345267</v>
@@ -9258,11 +9591,14 @@
         <v>0.6122622963187295</v>
       </c>
       <c r="O28">
-        <v>0.9175433765633235</v>
+        <v>0.9367050647257076</v>
       </c>
       <c r="P28">
         <v>18</v>
       </c>
+      <c r="Q28">
+        <v>35</v>
+      </c>
       <c r="R28">
         <v>44</v>
       </c>
@@ -9282,7 +9618,7 @@
         <v>13</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y28">
         <v>25</v>
@@ -9297,7 +9633,7 @@
         <v>16</v>
       </c>
       <c r="AC28">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29">
@@ -9307,7 +9643,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.9933853215063593</v>
+        <v>0.9933853215063598</v>
+      </c>
+      <c r="C29">
+        <v>0.1758816232500443</v>
       </c>
       <c r="D29">
         <v>0.1618478051932018</v>
@@ -9316,19 +9655,19 @@
         <v>1.249044272409676</v>
       </c>
       <c r="F29">
-        <v>0.2415054391916645</v>
+        <v>0.2429340691498245</v>
       </c>
       <c r="G29">
-        <v>0.7328930566627871</v>
+        <v>0.7322144858404214</v>
       </c>
       <c r="H29">
         <v>0.3651066728932982</v>
       </c>
       <c r="I29">
-        <v>1.18830318460131</v>
+        <v>1.188303184601311</v>
       </c>
       <c r="J29">
-        <v>0.5884343617437559</v>
+        <v>0.5952146045925314</v>
       </c>
       <c r="K29">
         <v>2.706161982978598</v>
@@ -9343,11 +9682,14 @@
         <v>1.149196061970363</v>
       </c>
       <c r="O29">
-        <v>0.9674649939214803</v>
+        <v>0.9071532194071061</v>
       </c>
       <c r="P29">
         <v>29</v>
       </c>
+      <c r="Q29">
+        <v>2</v>
+      </c>
       <c r="R29">
         <v>2</v>
       </c>
@@ -9367,7 +9709,7 @@
         <v>38</v>
       </c>
       <c r="X29">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y29">
         <v>49</v>
@@ -9382,7 +9724,7 @@
         <v>35</v>
       </c>
       <c r="AC29">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -9392,28 +9734,31 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.8880874069464858</v>
+        <v>0.888087406946486</v>
+      </c>
+      <c r="C30">
+        <v>1.118571074030278</v>
       </c>
       <c r="D30">
         <v>0.4856128370084132</v>
       </c>
       <c r="E30">
-        <v>0.7389540491862101</v>
+        <v>0.73895404918621</v>
       </c>
       <c r="F30">
-        <v>0.1762350825555669</v>
+        <v>0.1772776044940391</v>
       </c>
       <c r="G30">
-        <v>0.7280925660843037</v>
+        <v>0.7274184399388386</v>
       </c>
       <c r="H30">
         <v>0.2598423156434305</v>
       </c>
       <c r="I30">
-        <v>0.5188314697579541</v>
+        <v>0.5188314697579546</v>
       </c>
       <c r="J30">
-        <v>0.02268666575251414</v>
+        <v>0.02294807316382712</v>
       </c>
       <c r="K30">
         <v>2.063536464219674</v>
@@ -9428,11 +9773,14 @@
         <v>0.6865031388866196</v>
       </c>
       <c r="O30">
-        <v>0.6834946430047258</v>
+        <v>0.7170105071762545</v>
       </c>
       <c r="P30">
         <v>17</v>
       </c>
+      <c r="Q30">
+        <v>34</v>
+      </c>
       <c r="R30">
         <v>14</v>
       </c>
@@ -9467,7 +9815,7 @@
         <v>20</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
@@ -9477,7 +9825,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.5663090126677487</v>
+        <v>0.5663090126677489</v>
+      </c>
+      <c r="C31">
+        <v>0.9529379819702399</v>
       </c>
       <c r="D31">
         <v>1.021809984107647</v>
@@ -9486,19 +9837,19 @@
         <v>0.8054471394618585</v>
       </c>
       <c r="F31">
-        <v>0.414456692985003</v>
+        <v>0.4169084193309607</v>
       </c>
       <c r="G31">
-        <v>2.411681109139688</v>
+        <v>2.40968774008179</v>
       </c>
       <c r="H31">
         <v>1.182809990759922</v>
       </c>
       <c r="I31">
-        <v>0.6998452640681002</v>
+        <v>0.6998452640681005</v>
       </c>
       <c r="J31">
-        <v>1.365259800119051</v>
+        <v>1.380991024531314</v>
       </c>
       <c r="K31">
         <v>1.045731251457565</v>
@@ -9513,11 +9864,14 @@
         <v>1.540122714284886</v>
       </c>
       <c r="O31">
-        <v>1.158741766493601</v>
+        <v>1.144156058584136</v>
       </c>
       <c r="P31">
         <v>4</v>
       </c>
+      <c r="Q31">
+        <v>27</v>
+      </c>
       <c r="R31">
         <v>31</v>
       </c>
@@ -9537,7 +9891,7 @@
         <v>14</v>
       </c>
       <c r="X31">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Y31">
         <v>31</v>
@@ -9552,7 +9906,7 @@
         <v>40</v>
       </c>
       <c r="AC31">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="32">
@@ -9562,7 +9916,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.9207907847710753</v>
+        <v>0.9207907847710759</v>
+      </c>
+      <c r="C32">
+        <v>0.7320892852228001</v>
       </c>
       <c r="D32">
         <v>1.497489373793421</v>
@@ -9571,19 +9928,19 @@
         <v>1.165154993232086</v>
       </c>
       <c r="F32">
-        <v>1.313198972308154</v>
+        <v>1.32096722547522</v>
       </c>
       <c r="G32">
-        <v>0.4032452325406249</v>
+        <v>0.4028718759552778</v>
       </c>
       <c r="H32">
         <v>1.018441103420181</v>
       </c>
       <c r="I32">
-        <v>2.08354586418202</v>
+        <v>2.083545864182021</v>
       </c>
       <c r="J32">
-        <v>0.9431319862043048</v>
+        <v>0.9539992372022977</v>
       </c>
       <c r="K32">
         <v>2.328513863643056</v>
@@ -9598,11 +9955,14 @@
         <v>0.9091540997378189</v>
       </c>
       <c r="O32">
-        <v>1.133923527796497</v>
+        <v>1.104417982027729</v>
       </c>
       <c r="P32">
         <v>22</v>
       </c>
+      <c r="Q32">
+        <v>17</v>
+      </c>
       <c r="R32">
         <v>35</v>
       </c>
@@ -9610,7 +9970,7 @@
         <v>38</v>
       </c>
       <c r="T32">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U32">
         <v>13</v>
@@ -9622,7 +9982,7 @@
         <v>50</v>
       </c>
       <c r="X32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Y32">
         <v>47</v>
@@ -9637,7 +9997,7 @@
         <v>31</v>
       </c>
       <c r="AC32">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33">
@@ -9647,28 +10007,31 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.7146747276782675</v>
+        <v>0.7146747276782678</v>
+      </c>
+      <c r="C33">
+        <v>1.320346238231631</v>
       </c>
       <c r="D33">
         <v>0.9008056430204774</v>
       </c>
       <c r="E33">
-        <v>0.7554433295289702</v>
+        <v>0.75544332952897</v>
       </c>
       <c r="F33">
-        <v>0.9445430121601446</v>
+        <v>0.9501304740759474</v>
       </c>
       <c r="G33">
-        <v>1.752617561304861</v>
+        <v>1.751422527650714</v>
       </c>
       <c r="H33">
         <v>1.888366872322069</v>
       </c>
       <c r="I33">
-        <v>0.800513742872114</v>
+        <v>0.8005137428721144</v>
       </c>
       <c r="J33">
-        <v>1.930206038007687</v>
+        <v>1.952446863045644</v>
       </c>
       <c r="K33">
         <v>1.618618757774668</v>
@@ -9683,11 +10046,14 @@
         <v>2.536995027938452</v>
       </c>
       <c r="O33">
-        <v>1.457877143549872</v>
+        <v>1.449346554933054</v>
       </c>
       <c r="P33">
         <v>9</v>
       </c>
+      <c r="Q33">
+        <v>39</v>
+      </c>
       <c r="R33">
         <v>28</v>
       </c>
@@ -9695,7 +10061,7 @@
         <v>12</v>
       </c>
       <c r="T33">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U33">
         <v>48</v>
@@ -9707,7 +10073,7 @@
         <v>17</v>
       </c>
       <c r="X33">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y33">
         <v>43</v>
@@ -9734,26 +10100,29 @@
       <c r="B34">
         <v>1.050115226087627</v>
       </c>
+      <c r="C34">
+        <v>1.043957493125798</v>
+      </c>
       <c r="D34">
         <v>0.6260947128224265</v>
       </c>
       <c r="E34">
-        <v>1.067352540847432</v>
+        <v>1.067352540847431</v>
       </c>
       <c r="F34">
-        <v>0.4609919733134247</v>
+        <v>0.4637189799835486</v>
       </c>
       <c r="G34">
-        <v>0.6904256682512904</v>
+        <v>0.6908233278150376</v>
       </c>
       <c r="H34">
         <v>0.4166037311612161</v>
       </c>
       <c r="I34">
-        <v>0.7732155562520261</v>
+        <v>0.7732155562520265</v>
       </c>
       <c r="J34">
-        <v>0.5931342001702233</v>
+        <v>0.5999685969704898</v>
       </c>
       <c r="K34">
         <v>0.1524869193927312</v>
@@ -9768,11 +10137,14 @@
         <v>0.4517995247051952</v>
       </c>
       <c r="O34">
-        <v>0.6141890324257653</v>
+        <v>0.6480142265591631</v>
       </c>
       <c r="P34">
         <v>33</v>
       </c>
+      <c r="Q34">
+        <v>33</v>
+      </c>
       <c r="R34">
         <v>20</v>
       </c>
@@ -9783,7 +10155,7 @@
         <v>20</v>
       </c>
       <c r="U34">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="V34">
         <v>14</v>
@@ -9792,7 +10164,7 @@
         <v>16</v>
       </c>
       <c r="X34">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y34">
         <v>3</v>
@@ -9807,7 +10179,7 @@
         <v>9</v>
       </c>
       <c r="AC34">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -9817,28 +10189,31 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.7855463224368009</v>
+        <v>0.7855463224368014</v>
+      </c>
+      <c r="C35">
+        <v>1.563127379716164</v>
       </c>
       <c r="D35">
         <v>0.8126357937903714</v>
       </c>
       <c r="E35">
-        <v>0.990446409269094</v>
+        <v>0.9904464092690939</v>
       </c>
       <c r="F35">
-        <v>0.2135973122786426</v>
+        <v>0.2148608511882634</v>
       </c>
       <c r="G35">
-        <v>0.278639111704543</v>
+        <v>0.2808075849721724</v>
       </c>
       <c r="H35">
         <v>0.6624363412184066</v>
       </c>
       <c r="I35">
-        <v>0.4817056998586643</v>
+        <v>0.4817056998586647</v>
       </c>
       <c r="J35">
-        <v>0.1427620391268333</v>
+        <v>0.1444070166430984</v>
       </c>
       <c r="K35">
         <v>0.4072562490157211</v>
@@ -9853,11 +10228,14 @@
         <v>0.8493727302035224</v>
       </c>
       <c r="O35">
-        <v>0.6017654706950267</v>
+        <v>0.6761069244423078</v>
       </c>
       <c r="P35">
         <v>12</v>
       </c>
+      <c r="Q35">
+        <v>42</v>
+      </c>
       <c r="R35">
         <v>23</v>
       </c>
@@ -9892,7 +10270,7 @@
         <v>29</v>
       </c>
       <c r="AC35">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -9902,28 +10280,31 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.9849898888667064</v>
+        <v>0.984989888866707</v>
+      </c>
+      <c r="C36">
+        <v>0.6822823936696339</v>
       </c>
       <c r="D36">
         <v>0.3581695999214482</v>
       </c>
       <c r="E36">
-        <v>0.5558845533608686</v>
+        <v>0.5558845533608685</v>
       </c>
       <c r="F36">
-        <v>0.4321191164354282</v>
+        <v>0.4346753251787988</v>
       </c>
       <c r="G36">
-        <v>0.4518757170764494</v>
+        <v>0.4517132503965666</v>
       </c>
       <c r="H36">
         <v>0.9720222967986253</v>
       </c>
       <c r="I36">
-        <v>0.803813772674036</v>
+        <v>0.8038137726740364</v>
       </c>
       <c r="J36">
-        <v>0.6514729398341261</v>
+        <v>0.658979545546939</v>
       </c>
       <c r="K36">
         <v>0.9145738474256512</v>
@@ -9938,11 +10319,14 @@
         <v>0.6248545752838646</v>
       </c>
       <c r="O36">
-        <v>0.6529944949259185</v>
+        <v>0.6560089754274583</v>
       </c>
       <c r="P36">
         <v>27</v>
       </c>
+      <c r="Q36">
+        <v>14</v>
+      </c>
       <c r="R36">
         <v>9</v>
       </c>
@@ -9962,7 +10346,7 @@
         <v>18</v>
       </c>
       <c r="X36">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Y36">
         <v>30</v>
@@ -9977,7 +10361,7 @@
         <v>17</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -9987,28 +10371,31 @@
         </is>
       </c>
       <c r="B37">
-        <v>1.342283936010152</v>
+        <v>1.342283936010153</v>
+      </c>
+      <c r="C37">
+        <v>1.166807547316466</v>
       </c>
       <c r="D37">
         <v>2.053850222633794</v>
       </c>
       <c r="E37">
-        <v>0.9323078739683536</v>
+        <v>0.9323078739683537</v>
       </c>
       <c r="F37">
-        <v>0.7780550555694339</v>
+        <v>0.7826576548533456</v>
       </c>
       <c r="G37">
-        <v>0.4237968994875012</v>
+        <v>0.4236728065972077</v>
       </c>
       <c r="H37">
         <v>0.8523352299395638</v>
       </c>
       <c r="I37">
-        <v>1.323299022068647</v>
+        <v>1.323299022068648</v>
       </c>
       <c r="J37">
-        <v>1.231368569134855</v>
+        <v>1.245557030037006</v>
       </c>
       <c r="K37">
         <v>1.536831704864293</v>
@@ -10023,11 +10410,14 @@
         <v>1.879486515397073</v>
       </c>
       <c r="O37">
-        <v>1.324311056183038</v>
+        <v>1.313631322216053</v>
       </c>
       <c r="P37">
         <v>45</v>
       </c>
+      <c r="Q37">
+        <v>36</v>
+      </c>
       <c r="R37">
         <v>45</v>
       </c>
@@ -10035,7 +10425,7 @@
         <v>24</v>
       </c>
       <c r="T37">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U37">
         <v>16</v>
@@ -10047,7 +10437,7 @@
         <v>44</v>
       </c>
       <c r="X37">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Y37">
         <v>42</v>
@@ -10074,6 +10464,9 @@
       <c r="B38">
         <v>1.22797655688375</v>
       </c>
+      <c r="C38">
+        <v>0.711069125082632</v>
+      </c>
       <c r="D38">
         <v>0.8181193156521239</v>
       </c>
@@ -10081,19 +10474,19 @@
         <v>1.51176196971043</v>
       </c>
       <c r="F38">
-        <v>0.3124204347459719</v>
+        <v>0.31426856369128</v>
       </c>
       <c r="G38">
-        <v>0.7766152841757886</v>
+        <v>0.7765263986266333</v>
       </c>
       <c r="H38">
         <v>0.6620422593540402</v>
       </c>
       <c r="I38">
-        <v>1.171083250941861</v>
+        <v>1.171083250941862</v>
       </c>
       <c r="J38">
-        <v>0.5434142497455575</v>
+        <v>0.5496757477482259</v>
       </c>
       <c r="K38">
         <v>1.410039276362879</v>
@@ -10108,11 +10501,14 @@
         <v>1.322286229513459</v>
       </c>
       <c r="O38">
-        <v>1.033480105458542</v>
+        <v>1.009296240921843</v>
       </c>
       <c r="P38">
         <v>41</v>
       </c>
+      <c r="Q38">
+        <v>15</v>
+      </c>
       <c r="R38">
         <v>24</v>
       </c>
@@ -10132,7 +10528,7 @@
         <v>36</v>
       </c>
       <c r="X38">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y38">
         <v>40</v>
@@ -10147,7 +10543,7 @@
         <v>37</v>
       </c>
       <c r="AC38">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -10157,7 +10553,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>1.097425571421614</v>
+        <v>1.097425571421615</v>
+      </c>
+      <c r="C39">
+        <v>1.910590041389371</v>
       </c>
       <c r="D39">
         <v>1.573560701197665</v>
@@ -10166,19 +10565,19 @@
         <v>0.659472162983554</v>
       </c>
       <c r="F39">
-        <v>1.211984825647145</v>
+        <v>1.219154344630031</v>
       </c>
       <c r="G39">
-        <v>1.095931795988559</v>
+        <v>1.095447550479939</v>
       </c>
       <c r="H39">
         <v>1.009315818825589</v>
       </c>
       <c r="I39">
-        <v>0.9191920915796691</v>
+        <v>0.9191920915796696</v>
       </c>
       <c r="J39">
-        <v>1.242232323474834</v>
+        <v>1.256545962132506</v>
       </c>
       <c r="K39">
         <v>0.547544384411139</v>
@@ -10193,11 +10592,14 @@
         <v>1.427034128437979</v>
       </c>
       <c r="O39">
-        <v>1.01083000345395</v>
+        <v>1.081657614997593</v>
       </c>
       <c r="P39">
         <v>36</v>
       </c>
+      <c r="Q39">
+        <v>45</v>
+      </c>
       <c r="R39">
         <v>37</v>
       </c>
@@ -10205,7 +10607,7 @@
         <v>8</v>
       </c>
       <c r="T39">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="U39">
         <v>42</v>
@@ -10217,7 +10619,7 @@
         <v>21</v>
       </c>
       <c r="X39">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Y39">
         <v>15</v>
@@ -10232,7 +10634,7 @@
         <v>39</v>
       </c>
       <c r="AC39">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40">
@@ -10242,28 +10644,31 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.8237570403867901</v>
+        <v>0.8237570403867903</v>
+      </c>
+      <c r="C40">
+        <v>2.256322818982666</v>
       </c>
       <c r="D40">
         <v>5.938679943597233</v>
       </c>
       <c r="E40">
-        <v>0.4311016418149755</v>
+        <v>0.4311016418149753</v>
       </c>
       <c r="F40">
-        <v>0.2090120962215762</v>
+        <v>0.2102485111995552</v>
       </c>
       <c r="G40">
-        <v>0.8975861437332328</v>
+        <v>0.8967550869205639</v>
       </c>
       <c r="H40">
         <v>2.077299536734631</v>
       </c>
       <c r="I40">
-        <v>0.8222627078549861</v>
+        <v>0.8222627078549862</v>
       </c>
       <c r="J40">
-        <v>0.3410119985667141</v>
+        <v>0.3449413139074716</v>
       </c>
       <c r="K40">
         <v>0.6021157448222753</v>
@@ -10278,11 +10683,14 @@
         <v>0.4764908174799964</v>
       </c>
       <c r="O40">
-        <v>1.220725054059274</v>
+        <v>1.300719857015386</v>
       </c>
       <c r="P40">
         <v>15</v>
       </c>
+      <c r="Q40">
+        <v>47</v>
+      </c>
       <c r="R40">
         <v>49</v>
       </c>
@@ -10302,7 +10710,7 @@
         <v>20</v>
       </c>
       <c r="X40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y40">
         <v>18</v>
@@ -10317,7 +10725,7 @@
         <v>11</v>
       </c>
       <c r="AC40">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41">
@@ -10329,20 +10737,29 @@
       <c r="B41">
         <v>1.35233834515254</v>
       </c>
+      <c r="C41">
+        <v>0.8173032224292639</v>
+      </c>
       <c r="D41">
         <v>0.6307232493557264</v>
       </c>
       <c r="E41">
         <v>1.612680272655002</v>
       </c>
+      <c r="F41">
+        <v>0.68014950448373</v>
+      </c>
       <c r="G41">
-        <v>0.6134295802282576</v>
+        <v>0.613363794029307</v>
       </c>
       <c r="H41">
         <v>0.2112926097347227</v>
       </c>
       <c r="I41">
-        <v>1.22674868121919</v>
+        <v>1.226748681219191</v>
+      </c>
+      <c r="J41">
+        <v>0.2454456625265073</v>
       </c>
       <c r="K41">
         <v>0.1771522111885827</v>
@@ -10357,19 +10774,25 @@
         <v>0.01907495347097707</v>
       </c>
       <c r="O41">
-        <v>0.6524094546424738</v>
+        <v>0.6359174730511762</v>
       </c>
       <c r="P41">
         <v>46</v>
       </c>
+      <c r="Q41">
+        <v>24</v>
+      </c>
       <c r="R41">
         <v>21</v>
       </c>
       <c r="S41">
         <v>49</v>
       </c>
+      <c r="T41">
+        <v>28</v>
+      </c>
       <c r="U41">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V41">
         <v>6</v>
@@ -10377,6 +10800,9 @@
       <c r="W41">
         <v>41</v>
       </c>
+      <c r="X41">
+        <v>5</v>
+      </c>
       <c r="Y41">
         <v>4</v>
       </c>
@@ -10390,7 +10816,7 @@
         <v>1</v>
       </c>
       <c r="AC41">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -10402,26 +10828,29 @@
       <c r="B42">
         <v>1.293004340540811</v>
       </c>
+      <c r="C42">
+        <v>2.459356112777746</v>
+      </c>
       <c r="D42">
         <v>0.5898802269012373</v>
       </c>
       <c r="E42">
-        <v>0.8604833807274712</v>
+        <v>0.860483380727471</v>
       </c>
       <c r="F42">
-        <v>0.1390839374811421</v>
+        <v>0.1399066911236666</v>
       </c>
       <c r="G42">
-        <v>0.3656751734630771</v>
+        <v>0.3695475455196177</v>
       </c>
       <c r="H42">
         <v>0.5659891469148236</v>
       </c>
       <c r="I42">
-        <v>0.6562775323793202</v>
+        <v>0.6562775323793204</v>
       </c>
       <c r="J42">
-        <v>0.3485381708239607</v>
+        <v>0.3525542065857939</v>
       </c>
       <c r="K42">
         <v>1.791699252955132</v>
@@ -10436,11 +10865,14 @@
         <v>0.7465365505483805</v>
       </c>
       <c r="O42">
-        <v>0.8064878367587015</v>
+        <v>0.9343016396417742</v>
       </c>
       <c r="P42">
         <v>44</v>
       </c>
+      <c r="Q42">
+        <v>48</v>
+      </c>
       <c r="R42">
         <v>18</v>
       </c>
@@ -10460,7 +10892,7 @@
         <v>10</v>
       </c>
       <c r="X42">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y42">
         <v>44</v>
@@ -10475,7 +10907,7 @@
         <v>25</v>
       </c>
       <c r="AC42">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43">
@@ -10487,6 +10919,9 @@
       <c r="B43">
         <v>1.256941863008133</v>
       </c>
+      <c r="C43">
+        <v>0.6481090622846868</v>
+      </c>
       <c r="D43">
         <v>0.8863837956390725</v>
       </c>
@@ -10494,19 +10929,19 @@
         <v>0.8906047313178905</v>
       </c>
       <c r="F43">
-        <v>0.2898480383622668</v>
+        <v>0.2915626398731239</v>
       </c>
       <c r="G43">
-        <v>0.8588632279707169</v>
+        <v>0.8586410679947853</v>
       </c>
       <c r="H43">
         <v>0.3782484412276191</v>
       </c>
       <c r="I43">
-        <v>1.500300508025129</v>
+        <v>1.50030050802513</v>
       </c>
       <c r="J43">
-        <v>0.3478497061511003</v>
+        <v>0.3518578090694793</v>
       </c>
       <c r="K43">
         <v>0.8026123638939042</v>
@@ -10521,11 +10956,14 @@
         <v>0.04349941082066638</v>
       </c>
       <c r="O43">
-        <v>0.7219520444705136</v>
+        <v>0.7166949338757044</v>
       </c>
       <c r="P43">
         <v>42</v>
       </c>
+      <c r="Q43">
+        <v>12</v>
+      </c>
       <c r="R43">
         <v>27</v>
       </c>
@@ -10545,7 +10983,7 @@
         <v>47</v>
       </c>
       <c r="X43">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y43">
         <v>23</v>
@@ -10560,7 +10998,7 @@
         <v>2</v>
       </c>
       <c r="AC43">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
@@ -10570,7 +11008,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.270801027986324</v>
+        <v>1.270801027986325</v>
+      </c>
+      <c r="C44">
+        <v>0.1848635700854549</v>
       </c>
       <c r="D44">
         <v>0.408459232711797</v>
@@ -10579,10 +11020,10 @@
         <v>1.272556146654408</v>
       </c>
       <c r="F44">
-        <v>0.4742691189927093</v>
+        <v>0.477074666867287</v>
       </c>
       <c r="G44">
-        <v>1.054898407803877</v>
+        <v>1.054165452017108</v>
       </c>
       <c r="H44">
         <v>1.029429497288402</v>
@@ -10591,7 +11032,7 @@
         <v>1.015169395845254</v>
       </c>
       <c r="J44">
-        <v>0.9871244159823931</v>
+        <v>0.9984985703442875</v>
       </c>
       <c r="K44">
         <v>1.218317613049136</v>
@@ -10606,11 +11047,14 @@
         <v>0.9814003288984161</v>
       </c>
       <c r="O44">
-        <v>0.9736088463949777</v>
+        <v>0.9139704979442224</v>
       </c>
       <c r="P44">
         <v>43</v>
       </c>
+      <c r="Q44">
+        <v>3</v>
+      </c>
       <c r="R44">
         <v>12</v>
       </c>
@@ -10630,7 +11074,7 @@
         <v>26</v>
       </c>
       <c r="X44">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y44">
         <v>37</v>
@@ -10645,7 +11089,7 @@
         <v>34</v>
       </c>
       <c r="AC44">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
@@ -10655,28 +11099,31 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.5529476866353695</v>
+        <v>0.5529476866353696</v>
+      </c>
+      <c r="C45">
+        <v>0.3547049783781852</v>
       </c>
       <c r="D45">
         <v>0.3806778631998383</v>
       </c>
       <c r="E45">
-        <v>0.9136080822540718</v>
+        <v>0.9136080822540719</v>
       </c>
       <c r="F45">
-        <v>0.218674386426178</v>
+        <v>0.219967958863206</v>
       </c>
       <c r="G45">
-        <v>0.4605624981167081</v>
+        <v>0.4606007192993712</v>
       </c>
       <c r="H45">
         <v>0.2678596976371625</v>
       </c>
       <c r="I45">
-        <v>0.6831838268038157</v>
+        <v>0.6831838268038163</v>
       </c>
       <c r="J45">
-        <v>0.5172265976304684</v>
+        <v>0.523186348059366</v>
       </c>
       <c r="K45">
         <v>0.6702506537330017</v>
@@ -10691,11 +11138,14 @@
         <v>1.653297010800054</v>
       </c>
       <c r="O45">
-        <v>0.7255477285504215</v>
+        <v>0.6975822511562948</v>
       </c>
       <c r="P45">
         <v>3</v>
       </c>
+      <c r="Q45">
+        <v>6</v>
+      </c>
       <c r="R45">
         <v>10</v>
       </c>
@@ -10715,7 +11165,7 @@
         <v>12</v>
       </c>
       <c r="X45">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y45">
         <v>20</v>
@@ -10730,7 +11180,7 @@
         <v>41</v>
       </c>
       <c r="AC45">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
@@ -10740,7 +11190,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.7228179644192421</v>
+        <v>0.7228179644192425</v>
+      </c>
+      <c r="C46">
+        <v>0.3861266728913788</v>
       </c>
       <c r="D46">
         <v>1.85900469754476</v>
@@ -10749,19 +11202,19 @@
         <v>0.7440499932755942</v>
       </c>
       <c r="F46">
-        <v>0.4295565148850219</v>
+        <v>0.4320975645108256</v>
       </c>
       <c r="G46">
-        <v>0.352014488749877</v>
+        <v>0.3558371608495657</v>
       </c>
       <c r="H46">
         <v>0.6764160710565255</v>
       </c>
       <c r="I46">
-        <v>0.6014654507181533</v>
+        <v>0.6014654507181538</v>
       </c>
       <c r="J46">
-        <v>0.1636516625958365</v>
+        <v>0.1655373410795291</v>
       </c>
       <c r="K46">
         <v>3.009082439395557</v>
@@ -10776,11 +11229,14 @@
         <v>1.944782571331265</v>
       </c>
       <c r="O46">
-        <v>1.162181362748304</v>
+        <v>1.103119417390786</v>
       </c>
       <c r="P46">
         <v>10</v>
       </c>
+      <c r="Q46">
+        <v>7</v>
+      </c>
       <c r="R46">
         <v>43</v>
       </c>
@@ -10815,7 +11271,7 @@
         <v>46</v>
       </c>
       <c r="AC46">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="47">
@@ -10825,7 +11281,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.942782257913465</v>
+        <v>0.9427822579134656</v>
+      </c>
+      <c r="C47">
+        <v>0.520503585758064</v>
       </c>
       <c r="D47">
         <v>0.3883220361494183</v>
@@ -10834,19 +11293,19 @@
         <v>1.022062754293901</v>
       </c>
       <c r="F47">
-        <v>0.2469386531825635</v>
+        <v>0.2483994234200583</v>
       </c>
       <c r="G47">
-        <v>0.9332288359884892</v>
+        <v>0.9326884536105919</v>
       </c>
       <c r="H47">
         <v>0.4550887915703612</v>
       </c>
       <c r="I47">
-        <v>0.5994415189248987</v>
+        <v>0.5994415189248991</v>
       </c>
       <c r="J47">
-        <v>0.5866396843292735</v>
+        <v>0.5933992479833987</v>
       </c>
       <c r="K47">
         <v>0.4575686300745217</v>
@@ -10861,11 +11320,14 @@
         <v>0.3522272176062156</v>
       </c>
       <c r="O47">
-        <v>0.6036736561801794</v>
+        <v>0.597866723956457</v>
       </c>
       <c r="P47">
         <v>26</v>
       </c>
+      <c r="Q47">
+        <v>10</v>
+      </c>
       <c r="R47">
         <v>11</v>
       </c>
@@ -10885,7 +11347,7 @@
         <v>6</v>
       </c>
       <c r="X47">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y47">
         <v>10</v>
@@ -10900,7 +11362,7 @@
         <v>4</v>
       </c>
       <c r="AC47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -10910,7 +11372,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>1.120551187325926</v>
+        <v>1.120551187325927</v>
+      </c>
+      <c r="C48">
+        <v>0.7962105318713797</v>
       </c>
       <c r="D48">
         <v>0.9555205793186922</v>
@@ -10919,19 +11384,19 @@
         <v>1.090875621042141</v>
       </c>
       <c r="F48">
-        <v>1.892833563424254</v>
+        <v>1.904030655893764</v>
       </c>
       <c r="G48">
-        <v>0.9600687519596761</v>
+        <v>0.9600951908259265</v>
       </c>
       <c r="H48">
         <v>1.45941810748487</v>
       </c>
       <c r="I48">
-        <v>1.066146883901455</v>
+        <v>1.066146883901456</v>
       </c>
       <c r="J48">
-        <v>0.7982880896721158</v>
+        <v>0.8074863749238854</v>
       </c>
       <c r="K48">
         <v>1.371654499717176</v>
@@ -10946,11 +11411,14 @@
         <v>3.552237757270607</v>
       </c>
       <c r="O48">
-        <v>1.572351482681311</v>
+        <v>1.51421924158728</v>
       </c>
       <c r="P48">
         <v>38</v>
       </c>
+      <c r="Q48">
+        <v>23</v>
+      </c>
       <c r="R48">
         <v>29</v>
       </c>
@@ -10958,7 +11426,7 @@
         <v>34</v>
       </c>
       <c r="T48">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U48">
         <v>39</v>
@@ -10970,7 +11438,7 @@
         <v>31</v>
       </c>
       <c r="X48">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y48">
         <v>39</v>
@@ -10995,7 +11463,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>1.402761919633006</v>
+        <v>1.402761919633007</v>
+      </c>
+      <c r="C49">
+        <v>2.895362657482007</v>
       </c>
       <c r="D49">
         <v>1.540818191944081</v>
@@ -11004,19 +11475,19 @@
         <v>1.058931045958686</v>
       </c>
       <c r="F49">
-        <v>0.8707028852439385</v>
+        <v>0.8758535445031225</v>
       </c>
       <c r="G49">
-        <v>0.3516013569093909</v>
+        <v>0.354321392364114</v>
       </c>
       <c r="H49">
         <v>0.2593402274336268</v>
       </c>
       <c r="I49">
-        <v>1.132998619700501</v>
+        <v>1.132998619700502</v>
       </c>
       <c r="J49">
-        <v>0.8233094796890589</v>
+        <v>0.8327960742438848</v>
       </c>
       <c r="K49">
         <v>0.3421727982302419</v>
@@ -11031,11 +11502,14 @@
         <v>0.4300492717482075</v>
       </c>
       <c r="O49">
-        <v>0.7793966483719291</v>
+        <v>0.9434984405549147</v>
       </c>
       <c r="P49">
         <v>49</v>
       </c>
+      <c r="Q49">
+        <v>50</v>
+      </c>
       <c r="R49">
         <v>36</v>
       </c>
@@ -11043,7 +11517,7 @@
         <v>30</v>
       </c>
       <c r="T49">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="U49">
         <v>5</v>
@@ -11055,7 +11529,7 @@
         <v>34</v>
       </c>
       <c r="X49">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Y49">
         <v>7</v>
@@ -11070,7 +11544,7 @@
         <v>8</v>
       </c>
       <c r="AC49">
-        <v>17</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
@@ -11080,28 +11554,31 @@
         </is>
       </c>
       <c r="B50">
-        <v>0.6890047038716196</v>
+        <v>0.6890047038716197</v>
+      </c>
+      <c r="C50">
+        <v>0.9620866356225778</v>
       </c>
       <c r="D50">
         <v>1.821098148863753</v>
       </c>
       <c r="E50">
-        <v>0.7774879771906191</v>
+        <v>0.7774879771906189</v>
       </c>
       <c r="F50">
-        <v>0.6243281398914836</v>
+        <v>0.6280213647205253</v>
       </c>
       <c r="G50">
-        <v>0.4799949317810157</v>
+        <v>0.4804637114591407</v>
       </c>
       <c r="H50">
         <v>1.481736351233578</v>
       </c>
       <c r="I50">
-        <v>0.5814263417631045</v>
+        <v>0.5814263417631047</v>
       </c>
       <c r="J50">
-        <v>1.027667801124365</v>
+        <v>1.039509117186945</v>
       </c>
       <c r="K50">
         <v>0.7545286922937608</v>
@@ -11116,11 +11593,14 @@
         <v>2.118682587927029</v>
       </c>
       <c r="O50">
-        <v>1.00898001623074</v>
+        <v>1.006603857766246</v>
       </c>
       <c r="P50">
         <v>7</v>
       </c>
+      <c r="Q50">
+        <v>29</v>
+      </c>
       <c r="R50">
         <v>40</v>
       </c>
@@ -11140,7 +11620,7 @@
         <v>5</v>
       </c>
       <c r="X50">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Y50">
         <v>22</v>
@@ -11155,7 +11635,7 @@
         <v>47</v>
       </c>
       <c r="AC50">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51">
@@ -11165,7 +11645,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.6962561267170041</v>
+        <v>0.6962561267170043</v>
+      </c>
+      <c r="C51">
+        <v>0.9580183824834095</v>
       </c>
       <c r="D51">
         <v>0.1340862409324405</v>
@@ -11174,19 +11657,19 @@
         <v>1.45669379001046</v>
       </c>
       <c r="F51">
-        <v>0.6491883277860115</v>
+        <v>0.6530286135231241</v>
       </c>
       <c r="G51">
-        <v>0.3256254908742987</v>
+        <v>0.3293521551908259</v>
       </c>
       <c r="H51">
         <v>0.5263147742943812</v>
       </c>
       <c r="I51">
-        <v>1.811944766323545</v>
+        <v>1.811944766323546</v>
       </c>
       <c r="J51">
-        <v>1.628266069985939</v>
+        <v>1.647027787680688</v>
       </c>
       <c r="K51">
         <v>0.5176986370834736</v>
@@ -11201,11 +11684,14 @@
         <v>0.5814169713517231</v>
       </c>
       <c r="O51">
-        <v>0.8483294904498558</v>
+        <v>0.8587923796638515</v>
       </c>
       <c r="P51">
         <v>8</v>
       </c>
+      <c r="Q51">
+        <v>28</v>
+      </c>
       <c r="R51">
         <v>1</v>
       </c>
@@ -11225,7 +11711,7 @@
         <v>49</v>
       </c>
       <c r="X51">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Y51">
         <v>13</v>
@@ -11240,7 +11726,7 @@
         <v>14</v>
       </c>
       <c r="AC51">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
